--- a/research/traditional_assets/database/data/qatar/qatar_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_hospitals_healthcare_facilities.xlsx
@@ -1191,7 +1191,7 @@
         <v>0.0778465513115298</v>
       </c>
       <c r="X2">
-        <v>0.07589123526931291</v>
+        <v>0.0758912352693128</v>
       </c>
       <c r="Y2">
         <v>0.642330177931239</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07398212366612381</v>
+        <v>0.07394864154245769</v>
       </c>
       <c r="C2">
-        <v>409.663906103166</v>
+        <v>406.0650755012126</v>
       </c>
       <c r="D2">
-        <v>382.663906103166</v>
+        <v>383.1190755012125</v>
       </c>
       <c r="E2">
-        <v>-53.60000000000001</v>
+        <v>-49.54600000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.054</v>
       </c>
       <c r="G2">
         <v>27</v>
@@ -1451,28 +1451,28 @@
         <v>19.74</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2039162</v>
       </c>
       <c r="N2">
-        <v>19.74</v>
+        <v>19.5360838</v>
       </c>
       <c r="O2">
-        <v>1.974</v>
+        <v>1.95360838</v>
       </c>
       <c r="P2">
-        <v>17.766</v>
+        <v>17.58247542</v>
       </c>
       <c r="Q2">
-        <v>23.326</v>
+        <v>23.14247542</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07398212366612381</v>
+        <v>0.0742383247903613</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5700081124201052</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>96.80447164080149</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07394864154245769</v>
+        <v>0.07391515941879155</v>
       </c>
       <c r="C3">
-        <v>406.0650755012126</v>
+        <v>402.4673290146183</v>
       </c>
       <c r="D3">
-        <v>383.1190755012125</v>
+        <v>383.5753290146183</v>
       </c>
       <c r="E3">
-        <v>-49.54600000000001</v>
+        <v>-45.492</v>
       </c>
       <c r="F3">
-        <v>4.054</v>
+        <v>8.108000000000001</v>
       </c>
       <c r="G3">
         <v>27</v>
@@ -1533,28 +1533,28 @@
         <v>19.74</v>
       </c>
       <c r="M3">
-        <v>0.2039162</v>
+        <v>0.4078324</v>
       </c>
       <c r="N3">
-        <v>19.5360838</v>
+        <v>19.3321676</v>
       </c>
       <c r="O3">
-        <v>1.95360838</v>
+        <v>1.93321676</v>
       </c>
       <c r="P3">
-        <v>17.58247542</v>
+        <v>17.39895084</v>
       </c>
       <c r="Q3">
-        <v>23.14247542</v>
+        <v>22.95895084</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0742383247903613</v>
+        <v>0.07449975450897098</v>
       </c>
       <c r="T3">
-        <v>0.5700081124201052</v>
+        <v>0.5752481208078613</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>96.80447164080149</v>
+        <v>48.40223582040074</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07391515941879155</v>
+        <v>0.07388167729512543</v>
       </c>
       <c r="C4">
-        <v>402.4673290146183</v>
+        <v>398.8706705211945</v>
       </c>
       <c r="D4">
-        <v>383.5753290146183</v>
+        <v>384.0326705211945</v>
       </c>
       <c r="E4">
-        <v>-45.492</v>
+        <v>-41.43800000000001</v>
       </c>
       <c r="F4">
-        <v>8.108000000000001</v>
+        <v>12.162</v>
       </c>
       <c r="G4">
         <v>27</v>
@@ -1615,28 +1615,28 @@
         <v>19.74</v>
       </c>
       <c r="M4">
-        <v>0.4078324</v>
+        <v>0.6117486</v>
       </c>
       <c r="N4">
-        <v>19.3321676</v>
+        <v>19.1282514</v>
       </c>
       <c r="O4">
-        <v>1.93321676</v>
+        <v>1.91282514</v>
       </c>
       <c r="P4">
-        <v>17.39895084</v>
+        <v>17.21542626</v>
       </c>
       <c r="Q4">
-        <v>22.95895084</v>
+        <v>22.77542626</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07449975450897098</v>
+        <v>0.07476657453105715</v>
       </c>
       <c r="T4">
-        <v>0.5752481208078613</v>
+        <v>0.5805961706056741</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>48.40223582040074</v>
+        <v>32.2681572136005</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07388167729512543</v>
+        <v>0.07384819517145931</v>
       </c>
       <c r="C5">
-        <v>398.8706705211945</v>
+        <v>395.2751039172693</v>
       </c>
       <c r="D5">
-        <v>384.0326705211945</v>
+        <v>384.4911039172693</v>
       </c>
       <c r="E5">
-        <v>-41.43800000000001</v>
+        <v>-37.38400000000001</v>
       </c>
       <c r="F5">
-        <v>12.162</v>
+        <v>16.216</v>
       </c>
       <c r="G5">
         <v>27</v>
@@ -1697,28 +1697,28 @@
         <v>19.74</v>
       </c>
       <c r="M5">
-        <v>0.6117486</v>
+        <v>0.8156648</v>
       </c>
       <c r="N5">
-        <v>19.1282514</v>
+        <v>18.9243352</v>
       </c>
       <c r="O5">
-        <v>1.91282514</v>
+        <v>1.89243352</v>
       </c>
       <c r="P5">
-        <v>17.21542626</v>
+        <v>17.03190168</v>
       </c>
       <c r="Q5">
-        <v>22.77542626</v>
+        <v>22.59190168</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07476657453105715</v>
+        <v>0.07503895330360345</v>
       </c>
       <c r="T5">
-        <v>0.5805961706056741</v>
+        <v>0.5860556381076082</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.2681572136005</v>
+        <v>24.20111791020037</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07384819517145931</v>
+        <v>0.07381471304779318</v>
       </c>
       <c r="C6">
-        <v>395.2751039172693</v>
+        <v>391.6806331177978</v>
       </c>
       <c r="D6">
-        <v>384.4911039172693</v>
+        <v>384.9506331177977</v>
       </c>
       <c r="E6">
-        <v>-37.38400000000001</v>
+        <v>-33.33000000000001</v>
       </c>
       <c r="F6">
-        <v>16.216</v>
+        <v>20.27</v>
       </c>
       <c r="G6">
         <v>27</v>
@@ -1779,28 +1779,28 @@
         <v>19.74</v>
       </c>
       <c r="M6">
-        <v>0.8156648</v>
+        <v>1.019581</v>
       </c>
       <c r="N6">
-        <v>18.9243352</v>
+        <v>18.720419</v>
       </c>
       <c r="O6">
-        <v>1.89243352</v>
+        <v>1.8720419</v>
       </c>
       <c r="P6">
-        <v>17.03190168</v>
+        <v>16.8483771</v>
       </c>
       <c r="Q6">
-        <v>22.59190168</v>
+        <v>22.4083771</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07503895330360345</v>
+        <v>0.07531706636609808</v>
       </c>
       <c r="T6">
-        <v>0.5860556381076082</v>
+        <v>0.5916300417674776</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.20111791020037</v>
+        <v>19.3608943281603</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07381471304779318</v>
+        <v>0.07378123092412706</v>
       </c>
       <c r="C7">
-        <v>391.6806331177978</v>
+        <v>388.0872620564728</v>
       </c>
       <c r="D7">
-        <v>384.9506331177977</v>
+        <v>385.4112620564728</v>
       </c>
       <c r="E7">
-        <v>-33.33000000000001</v>
+        <v>-29.276</v>
       </c>
       <c r="F7">
-        <v>20.27</v>
+        <v>24.32400000000001</v>
       </c>
       <c r="G7">
         <v>27</v>
@@ -1861,28 +1861,28 @@
         <v>19.74</v>
       </c>
       <c r="M7">
-        <v>1.019581</v>
+        <v>1.2234972</v>
       </c>
       <c r="N7">
-        <v>18.720419</v>
+        <v>18.5165028</v>
       </c>
       <c r="O7">
-        <v>1.8720419</v>
+        <v>1.85165028</v>
       </c>
       <c r="P7">
-        <v>16.8483771</v>
+        <v>16.66485252</v>
       </c>
       <c r="Q7">
-        <v>22.4083771</v>
+        <v>22.22485252</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07531706636609808</v>
+        <v>0.07560109672779475</v>
       </c>
       <c r="T7">
-        <v>0.5916300417674776</v>
+        <v>0.5973230497605359</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.3608943281603</v>
+        <v>16.13407860680024</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07378123092412706</v>
+        <v>0.07374774880046095</v>
       </c>
       <c r="C8">
-        <v>388.0872620564728</v>
+        <v>384.4949946858383</v>
       </c>
       <c r="D8">
-        <v>385.4112620564728</v>
+        <v>385.8729946858383</v>
       </c>
       <c r="E8">
-        <v>-29.27600000000001</v>
+        <v>-25.22200000000001</v>
       </c>
       <c r="F8">
-        <v>24.324</v>
+        <v>28.378</v>
       </c>
       <c r="G8">
         <v>27</v>
@@ -1943,28 +1943,28 @@
         <v>19.74</v>
       </c>
       <c r="M8">
-        <v>1.2234972</v>
+        <v>1.4274134</v>
       </c>
       <c r="N8">
-        <v>18.5165028</v>
+        <v>18.3125866</v>
       </c>
       <c r="O8">
-        <v>1.85165028</v>
+        <v>1.83125866</v>
       </c>
       <c r="P8">
-        <v>16.66485252</v>
+        <v>16.48132794</v>
       </c>
       <c r="Q8">
-        <v>22.22485252</v>
+        <v>22.04132794</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07560109672779475</v>
+        <v>0.07589123526931284</v>
       </c>
       <c r="T8">
-        <v>0.5973230497605359</v>
+        <v>0.6031384880330145</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.13407860680024</v>
+        <v>13.82921023440021</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07374774880046095</v>
+        <v>0.07382226667679483</v>
       </c>
       <c r="C9">
-        <v>384.4949946858383</v>
+        <v>379.414866556011</v>
       </c>
       <c r="D9">
-        <v>385.8729946858383</v>
+        <v>384.846866556011</v>
       </c>
       <c r="E9">
-        <v>-25.222</v>
+        <v>-21.16800000000001</v>
       </c>
       <c r="F9">
-        <v>28.378</v>
+        <v>32.432</v>
       </c>
       <c r="G9">
         <v>27</v>
@@ -2025,45 +2025,45 @@
         <v>19.74</v>
       </c>
       <c r="M9">
-        <v>1.4274134</v>
+        <v>1.6799776</v>
       </c>
       <c r="N9">
-        <v>18.3125866</v>
+        <v>18.0600224</v>
       </c>
       <c r="O9">
-        <v>1.83125866</v>
+        <v>1.80600224</v>
       </c>
       <c r="P9">
-        <v>16.48132794</v>
+        <v>16.25402016</v>
       </c>
       <c r="Q9">
-        <v>22.04132794</v>
+        <v>21.81402016</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07589123526931285</v>
+        <v>0.07618768117042915</v>
       </c>
       <c r="T9">
-        <v>0.6031384880330146</v>
+        <v>0.6090803488766342</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.1</v>
       </c>
       <c r="W9">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.82921023440021</v>
+        <v>11.75015666875558</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07382226667679483</v>
+        <v>0.07380228455312869</v>
       </c>
       <c r="C10">
-        <v>379.414866556011</v>
+        <v>375.63548906638</v>
       </c>
       <c r="D10">
-        <v>384.846866556011</v>
+        <v>385.12148906638</v>
       </c>
       <c r="E10">
-        <v>-21.16800000000001</v>
+        <v>-17.114</v>
       </c>
       <c r="F10">
-        <v>32.432</v>
+        <v>36.486</v>
       </c>
       <c r="G10">
         <v>27</v>
@@ -2107,28 +2107,28 @@
         <v>19.74</v>
       </c>
       <c r="M10">
-        <v>1.6799776</v>
+        <v>1.8899748</v>
       </c>
       <c r="N10">
-        <v>18.0600224</v>
+        <v>17.8500252</v>
       </c>
       <c r="O10">
-        <v>1.80600224</v>
+        <v>1.78500252</v>
       </c>
       <c r="P10">
-        <v>16.25402016</v>
+        <v>16.06502268</v>
       </c>
       <c r="Q10">
-        <v>21.81402016</v>
+        <v>21.62502268</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07618768117042915</v>
+        <v>0.07649064236607549</v>
       </c>
       <c r="T10">
-        <v>0.6090803488766342</v>
+        <v>0.6151528000684652</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.75015666875558</v>
+        <v>10.44458370556052</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07380228455312869</v>
+        <v>0.07393530242946257</v>
       </c>
       <c r="C11">
-        <v>375.63548906638</v>
+        <v>369.7607145168764</v>
       </c>
       <c r="D11">
-        <v>385.12148906638</v>
+        <v>383.3007145168764</v>
       </c>
       <c r="E11">
-        <v>-17.114</v>
+        <v>-13.06000000000001</v>
       </c>
       <c r="F11">
-        <v>36.486</v>
+        <v>40.54</v>
       </c>
       <c r="G11">
         <v>27</v>
@@ -2189,45 +2189,45 @@
         <v>19.74</v>
       </c>
       <c r="M11">
-        <v>1.8899748</v>
+        <v>2.16889</v>
       </c>
       <c r="N11">
-        <v>17.8500252</v>
+        <v>17.57111</v>
       </c>
       <c r="O11">
-        <v>1.78500252</v>
+        <v>1.757111</v>
       </c>
       <c r="P11">
-        <v>16.06502268</v>
+        <v>15.813999</v>
       </c>
       <c r="Q11">
-        <v>21.62502268</v>
+        <v>21.373999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07649064236607549</v>
+        <v>0.07680033603273619</v>
       </c>
       <c r="T11">
-        <v>0.6151528000684652</v>
+        <v>0.6213601946201147</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.1</v>
       </c>
       <c r="W11">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.44458370556052</v>
+        <v>9.101429763611803</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07393530242946257</v>
+        <v>0.07393062030579643</v>
       </c>
       <c r="C12">
-        <v>369.7607145168764</v>
+        <v>365.7705119492536</v>
       </c>
       <c r="D12">
-        <v>383.3007145168764</v>
+        <v>383.3645119492536</v>
       </c>
       <c r="E12">
-        <v>-13.06</v>
+        <v>-9.006000000000007</v>
       </c>
       <c r="F12">
-        <v>40.54000000000001</v>
+        <v>44.594</v>
       </c>
       <c r="G12">
         <v>27</v>
@@ -2271,28 +2271,28 @@
         <v>19.74</v>
       </c>
       <c r="M12">
-        <v>2.16889</v>
+        <v>2.385779</v>
       </c>
       <c r="N12">
-        <v>17.57111</v>
+        <v>17.354221</v>
       </c>
       <c r="O12">
-        <v>1.757111</v>
+        <v>1.7354221</v>
       </c>
       <c r="P12">
-        <v>15.813999</v>
+        <v>15.6187989</v>
       </c>
       <c r="Q12">
-        <v>21.373999</v>
+        <v>21.1787989</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07680033603273619</v>
+        <v>0.07711698910763645</v>
       </c>
       <c r="T12">
-        <v>0.6213601946201147</v>
+        <v>0.6277070811841607</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.101429763611801</v>
+        <v>8.274027057828912</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07393062030579643</v>
+        <v>0.07401233818213034</v>
       </c>
       <c r="C13">
-        <v>365.7705119492536</v>
+        <v>360.606085242469</v>
       </c>
       <c r="D13">
-        <v>383.3645119492536</v>
+        <v>382.254085242469</v>
       </c>
       <c r="E13">
-        <v>-9.006000000000007</v>
+        <v>-4.952000000000005</v>
       </c>
       <c r="F13">
-        <v>44.594</v>
+        <v>48.648</v>
       </c>
       <c r="G13">
         <v>27</v>
@@ -2353,45 +2353,45 @@
         <v>19.74</v>
       </c>
       <c r="M13">
-        <v>2.385779</v>
+        <v>2.6415864</v>
       </c>
       <c r="N13">
-        <v>17.354221</v>
+        <v>17.0984136</v>
       </c>
       <c r="O13">
-        <v>1.7354221</v>
+        <v>1.70984136</v>
       </c>
       <c r="P13">
-        <v>15.6187989</v>
+        <v>15.38857224</v>
       </c>
       <c r="Q13">
-        <v>21.1787989</v>
+        <v>20.94857224</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07711698910763645</v>
+        <v>0.07744083884332992</v>
       </c>
       <c r="T13">
-        <v>0.6277070811841607</v>
+        <v>0.6341982151701171</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.1</v>
       </c>
       <c r="W13">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>8.274027057828912</v>
+        <v>7.472782264475619</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07401233818213034</v>
+        <v>0.0740148560584642</v>
       </c>
       <c r="C14">
-        <v>360.606085242469</v>
+        <v>356.5179731239184</v>
       </c>
       <c r="D14">
-        <v>382.254085242469</v>
+        <v>382.2199731239184</v>
       </c>
       <c r="E14">
-        <v>-4.952000000000005</v>
+        <v>-0.8980000000000032</v>
       </c>
       <c r="F14">
-        <v>48.648</v>
+        <v>52.70200000000001</v>
       </c>
       <c r="G14">
         <v>27</v>
@@ -2435,28 +2435,28 @@
         <v>19.74</v>
       </c>
       <c r="M14">
-        <v>2.6415864</v>
+        <v>2.861718600000001</v>
       </c>
       <c r="N14">
-        <v>17.0984136</v>
+        <v>16.8782814</v>
       </c>
       <c r="O14">
-        <v>1.70984136</v>
+        <v>1.68782814</v>
       </c>
       <c r="P14">
-        <v>15.38857224</v>
+        <v>15.19045326</v>
       </c>
       <c r="Q14">
-        <v>20.94857224</v>
+        <v>20.75045326</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07744083884332992</v>
+        <v>0.07777213340053356</v>
       </c>
       <c r="T14">
-        <v>0.6341982151701171</v>
+        <v>0.6408385706270148</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.472782264475619</v>
+        <v>6.897952859515956</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0740148560584642</v>
+        <v>0.07401737393479807</v>
       </c>
       <c r="C15">
-        <v>356.5179731239184</v>
+        <v>352.4298670931132</v>
       </c>
       <c r="D15">
-        <v>382.2199731239184</v>
+        <v>382.1858670931132</v>
       </c>
       <c r="E15">
-        <v>-0.8980000000000032</v>
+        <v>3.155999999999999</v>
       </c>
       <c r="F15">
-        <v>52.70200000000001</v>
+        <v>56.75600000000001</v>
       </c>
       <c r="G15">
         <v>27</v>
@@ -2517,28 +2517,28 @@
         <v>19.74</v>
       </c>
       <c r="M15">
-        <v>2.861718600000001</v>
+        <v>3.081850800000001</v>
       </c>
       <c r="N15">
-        <v>16.8782814</v>
+        <v>16.6581492</v>
       </c>
       <c r="O15">
-        <v>1.68782814</v>
+        <v>1.66581492</v>
       </c>
       <c r="P15">
-        <v>15.19045326</v>
+        <v>14.99233428</v>
       </c>
       <c r="Q15">
-        <v>20.75045326</v>
+        <v>20.55233428</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07777213340053356</v>
+        <v>0.07811113248232335</v>
       </c>
       <c r="T15">
-        <v>0.6408385706270148</v>
+        <v>0.6476333529550032</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.897952859515956</v>
+        <v>6.405241940979102</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07401737393479807</v>
+        <v>0.07415489181113195</v>
       </c>
       <c r="C16">
-        <v>352.4298670931132</v>
+        <v>346.5223107770622</v>
       </c>
       <c r="D16">
-        <v>382.1858670931132</v>
+        <v>380.3323107770622</v>
       </c>
       <c r="E16">
-        <v>3.155999999999999</v>
+        <v>7.210000000000008</v>
       </c>
       <c r="F16">
-        <v>56.75600000000001</v>
+        <v>60.81000000000002</v>
       </c>
       <c r="G16">
         <v>27</v>
@@ -2599,45 +2599,45 @@
         <v>19.74</v>
       </c>
       <c r="M16">
-        <v>3.081850800000001</v>
+        <v>3.362793000000001</v>
       </c>
       <c r="N16">
-        <v>16.6581492</v>
+        <v>16.377207</v>
       </c>
       <c r="O16">
-        <v>1.66581492</v>
+        <v>1.6377207</v>
       </c>
       <c r="P16">
-        <v>14.99233428</v>
+        <v>14.7394863</v>
       </c>
       <c r="Q16">
-        <v>20.55233428</v>
+        <v>20.2994863</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07811113248232335</v>
+        <v>0.07845810801309641</v>
       </c>
       <c r="T16">
-        <v>0.6476333529550032</v>
+        <v>0.6545880125142386</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.1</v>
       </c>
       <c r="W16">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.405241940979102</v>
+        <v>5.870120462365658</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07415489181113195</v>
+        <v>0.07416640968746584</v>
       </c>
       <c r="C17">
-        <v>346.5223107770622</v>
+        <v>342.3138809225414</v>
       </c>
       <c r="D17">
-        <v>380.3323107770622</v>
+        <v>380.1778809225414</v>
       </c>
       <c r="E17">
-        <v>7.209999999999994</v>
+        <v>11.264</v>
       </c>
       <c r="F17">
-        <v>60.81</v>
+        <v>64.864</v>
       </c>
       <c r="G17">
         <v>27</v>
@@ -2681,28 +2681,28 @@
         <v>19.74</v>
       </c>
       <c r="M17">
-        <v>3.362793</v>
+        <v>3.5869792</v>
       </c>
       <c r="N17">
-        <v>16.377207</v>
+        <v>16.1530208</v>
       </c>
       <c r="O17">
-        <v>1.6377207</v>
+        <v>1.61530208</v>
       </c>
       <c r="P17">
-        <v>14.7394863</v>
+        <v>14.53771872</v>
       </c>
       <c r="Q17">
-        <v>20.2994863</v>
+        <v>20.09771872</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07845810801309641</v>
+        <v>0.07881334486603075</v>
       </c>
       <c r="T17">
-        <v>0.6545880125142386</v>
+        <v>0.6617082592058364</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.870120462365659</v>
+        <v>5.503237933467805</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07416640968746584</v>
+        <v>0.07417792756379971</v>
       </c>
       <c r="C18">
-        <v>342.3138809225414</v>
+        <v>338.1055764262919</v>
       </c>
       <c r="D18">
-        <v>380.1778809225414</v>
+        <v>380.0235764262919</v>
       </c>
       <c r="E18">
-        <v>11.264</v>
+        <v>15.318</v>
       </c>
       <c r="F18">
-        <v>64.864</v>
+        <v>68.91800000000001</v>
       </c>
       <c r="G18">
         <v>27</v>
@@ -2763,28 +2763,28 @@
         <v>19.74</v>
       </c>
       <c r="M18">
-        <v>3.5869792</v>
+        <v>3.811165400000001</v>
       </c>
       <c r="N18">
-        <v>16.1530208</v>
+        <v>15.9288346</v>
       </c>
       <c r="O18">
-        <v>1.61530208</v>
+        <v>1.59288346</v>
       </c>
       <c r="P18">
-        <v>14.53771872</v>
+        <v>14.33595114</v>
       </c>
       <c r="Q18">
-        <v>20.09771872</v>
+        <v>19.89595114</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07881334486603075</v>
+        <v>0.07917714164313217</v>
       </c>
       <c r="T18">
-        <v>0.6617082592058364</v>
+        <v>0.6690000781068705</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.503237933467805</v>
+        <v>5.179518055028522</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07417792756379971</v>
+        <v>0.07418944544013356</v>
       </c>
       <c r="C19">
-        <v>338.1055764262919</v>
+        <v>333.8973971357362</v>
       </c>
       <c r="D19">
-        <v>380.0235764262919</v>
+        <v>379.8693971357362</v>
       </c>
       <c r="E19">
-        <v>15.318</v>
+        <v>19.372</v>
       </c>
       <c r="F19">
-        <v>68.91800000000001</v>
+        <v>72.97200000000001</v>
       </c>
       <c r="G19">
         <v>27</v>
@@ -2845,28 +2845,28 @@
         <v>19.74</v>
       </c>
       <c r="M19">
-        <v>3.811165400000001</v>
+        <v>4.0353516</v>
       </c>
       <c r="N19">
-        <v>15.9288346</v>
+        <v>15.7046484</v>
       </c>
       <c r="O19">
-        <v>1.59288346</v>
+        <v>1.57046484</v>
       </c>
       <c r="P19">
-        <v>14.33595114</v>
+        <v>14.13418356</v>
       </c>
       <c r="Q19">
-        <v>19.89595114</v>
+        <v>19.69418356</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07917714164313217</v>
+        <v>0.07954981151235802</v>
       </c>
       <c r="T19">
-        <v>0.6690000781068705</v>
+        <v>0.6764697462493932</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.179518055028522</v>
+        <v>4.891767051971383</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07418944544013358</v>
+        <v>0.07420096331646746</v>
       </c>
       <c r="C20">
-        <v>333.897397135736</v>
+        <v>329.6893428985441</v>
       </c>
       <c r="D20">
-        <v>379.8693971357361</v>
+        <v>379.7153428985441</v>
       </c>
       <c r="E20">
-        <v>19.372</v>
+        <v>23.426</v>
       </c>
       <c r="F20">
-        <v>72.97200000000001</v>
+        <v>77.02600000000001</v>
       </c>
       <c r="G20">
         <v>27</v>
@@ -2927,28 +2927,28 @@
         <v>19.74</v>
       </c>
       <c r="M20">
-        <v>4.0353516</v>
+        <v>4.2595378</v>
       </c>
       <c r="N20">
-        <v>15.7046484</v>
+        <v>15.4804622</v>
       </c>
       <c r="O20">
-        <v>1.57046484</v>
+        <v>1.54804622</v>
       </c>
       <c r="P20">
-        <v>14.13418356</v>
+        <v>13.93241598</v>
       </c>
       <c r="Q20">
-        <v>19.69418356</v>
+        <v>19.49241598</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07954981151235802</v>
+        <v>0.07993168310674995</v>
       </c>
       <c r="T20">
-        <v>0.6764697462493932</v>
+        <v>0.6841238506423485</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.891767051971383</v>
+        <v>4.634305628183414</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07420096331646746</v>
+        <v>0.07466248119280133</v>
       </c>
       <c r="C21">
-        <v>329.6893428985441</v>
+        <v>319.5636050775547</v>
       </c>
       <c r="D21">
-        <v>379.7153428985441</v>
+        <v>373.6436050775547</v>
       </c>
       <c r="E21">
-        <v>23.426</v>
+        <v>27.48</v>
       </c>
       <c r="F21">
-        <v>77.02600000000001</v>
+        <v>81.08000000000001</v>
       </c>
       <c r="G21">
         <v>27</v>
@@ -3009,45 +3009,45 @@
         <v>19.74</v>
       </c>
       <c r="M21">
-        <v>4.2595378</v>
+        <v>4.686424000000001</v>
       </c>
       <c r="N21">
-        <v>15.4804622</v>
+        <v>15.053576</v>
       </c>
       <c r="O21">
-        <v>1.54804622</v>
+        <v>1.5053576</v>
       </c>
       <c r="P21">
-        <v>13.93241598</v>
+        <v>13.5482184</v>
       </c>
       <c r="Q21">
-        <v>19.49241598</v>
+        <v>19.1082184</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07993168310674995</v>
+        <v>0.08032310149100166</v>
       </c>
       <c r="T21">
-        <v>0.6841238506423485</v>
+        <v>0.6919693076451278</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.634305628183414</v>
+        <v>4.212166888868783</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07466248119280133</v>
+        <v>0.0746964990691352</v>
       </c>
       <c r="C22">
-        <v>319.5636050775547</v>
+        <v>315.0697399603287</v>
       </c>
       <c r="D22">
-        <v>373.6436050775547</v>
+        <v>373.2037399603287</v>
       </c>
       <c r="E22">
-        <v>27.48</v>
+        <v>31.53400000000001</v>
       </c>
       <c r="F22">
-        <v>81.08000000000001</v>
+        <v>85.13400000000001</v>
       </c>
       <c r="G22">
         <v>27</v>
@@ -3091,28 +3091,28 @@
         <v>19.74</v>
       </c>
       <c r="M22">
-        <v>4.686424000000001</v>
+        <v>4.920745200000002</v>
       </c>
       <c r="N22">
-        <v>15.053576</v>
+        <v>14.8192548</v>
       </c>
       <c r="O22">
-        <v>1.5053576</v>
+        <v>1.48192548</v>
       </c>
       <c r="P22">
-        <v>13.5482184</v>
+        <v>13.33732932</v>
       </c>
       <c r="Q22">
-        <v>19.1082184</v>
+        <v>18.89732932</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08032310149100166</v>
+        <v>0.08072442920143696</v>
       </c>
       <c r="T22">
-        <v>0.6919693076451278</v>
+        <v>0.7000133838125343</v>
       </c>
       <c r="U22">
         <v>0.0578</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.212166888868783</v>
+        <v>4.011587513208364</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0746964990691352</v>
+        <v>0.0754235169454691</v>
       </c>
       <c r="C23">
-        <v>315.0697399603287</v>
+        <v>301.8566049742538</v>
       </c>
       <c r="D23">
-        <v>373.2037399603287</v>
+        <v>364.0446049742538</v>
       </c>
       <c r="E23">
-        <v>31.53399999999999</v>
+        <v>35.58799999999999</v>
       </c>
       <c r="F23">
-        <v>85.134</v>
+        <v>89.188</v>
       </c>
       <c r="G23">
         <v>27</v>
@@ -3173,45 +3173,45 @@
         <v>19.74</v>
       </c>
       <c r="M23">
-        <v>4.920745200000001</v>
+        <v>5.4672244</v>
       </c>
       <c r="N23">
-        <v>14.8192548</v>
+        <v>14.2727756</v>
       </c>
       <c r="O23">
-        <v>1.48192548</v>
+        <v>1.42727756</v>
       </c>
       <c r="P23">
-        <v>13.33732932</v>
+        <v>12.84549804</v>
       </c>
       <c r="Q23">
-        <v>18.89732932</v>
+        <v>18.40549804</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08072442920143696</v>
+        <v>0.08113604736598601</v>
       </c>
       <c r="T23">
-        <v>0.7000133838125343</v>
+        <v>0.7082637183432077</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.1</v>
       </c>
       <c r="W23">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.011587513208365</v>
+        <v>3.610607239754052</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0754235169454691</v>
+        <v>0.07606863482180296</v>
       </c>
       <c r="C24">
-        <v>301.8566049742538</v>
+        <v>290.0436926931283</v>
       </c>
       <c r="D24">
-        <v>364.0446049742538</v>
+        <v>356.2856926931283</v>
       </c>
       <c r="E24">
-        <v>35.58799999999999</v>
+        <v>39.64200000000001</v>
       </c>
       <c r="F24">
-        <v>89.188</v>
+        <v>93.24200000000002</v>
       </c>
       <c r="G24">
         <v>27</v>
@@ -3255,45 +3255,45 @@
         <v>19.74</v>
       </c>
       <c r="M24">
-        <v>5.4672244</v>
+        <v>5.976812200000001</v>
       </c>
       <c r="N24">
-        <v>14.2727756</v>
+        <v>13.7631878</v>
       </c>
       <c r="O24">
-        <v>1.42727756</v>
+        <v>1.37631878</v>
       </c>
       <c r="P24">
-        <v>12.84549804</v>
+        <v>12.38686902</v>
       </c>
       <c r="Q24">
-        <v>18.40549804</v>
+        <v>17.94686902</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08113604736598601</v>
+        <v>0.08155835691143241</v>
       </c>
       <c r="T24">
-        <v>0.7082637183432077</v>
+        <v>0.7167283472772752</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.610607239754052</v>
+        <v>3.302763971737308</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07606863482180296</v>
+        <v>0.07615935269813684</v>
       </c>
       <c r="C25">
-        <v>290.0436926931283</v>
+        <v>284.9250625697315</v>
       </c>
       <c r="D25">
-        <v>356.2856926931283</v>
+        <v>355.2210625697315</v>
       </c>
       <c r="E25">
-        <v>39.64200000000001</v>
+        <v>43.69600000000001</v>
       </c>
       <c r="F25">
-        <v>93.24200000000002</v>
+        <v>97.29600000000002</v>
       </c>
       <c r="G25">
         <v>27</v>
@@ -3337,28 +3337,28 @@
         <v>19.74</v>
       </c>
       <c r="M25">
-        <v>5.976812200000001</v>
+        <v>6.236673600000001</v>
       </c>
       <c r="N25">
-        <v>13.7631878</v>
+        <v>13.5033264</v>
       </c>
       <c r="O25">
-        <v>1.37631878</v>
+        <v>1.35033264</v>
       </c>
       <c r="P25">
-        <v>12.38686902</v>
+        <v>12.15299376</v>
       </c>
       <c r="Q25">
-        <v>17.94686902</v>
+        <v>17.71299376</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08155835691143241</v>
+        <v>0.08199177986596952</v>
       </c>
       <c r="T25">
-        <v>0.7167283472772752</v>
+        <v>0.7254157296043444</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.302763971737308</v>
+        <v>3.165148806248253</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07615935269813684</v>
+        <v>0.07625007057447072</v>
       </c>
       <c r="C26">
-        <v>284.9250625697315</v>
+        <v>279.8127760102116</v>
       </c>
       <c r="D26">
-        <v>355.2210625697315</v>
+        <v>354.1627760102116</v>
       </c>
       <c r="E26">
-        <v>43.696</v>
+        <v>47.75</v>
       </c>
       <c r="F26">
-        <v>97.29600000000001</v>
+        <v>101.35</v>
       </c>
       <c r="G26">
         <v>27</v>
@@ -3419,28 +3419,28 @@
         <v>19.74</v>
       </c>
       <c r="M26">
-        <v>6.2366736</v>
+        <v>6.496535000000001</v>
       </c>
       <c r="N26">
-        <v>13.5033264</v>
+        <v>13.243465</v>
       </c>
       <c r="O26">
-        <v>1.35033264</v>
+        <v>1.3243465</v>
       </c>
       <c r="P26">
-        <v>12.15299376</v>
+        <v>11.9191185</v>
       </c>
       <c r="Q26">
-        <v>17.71299376</v>
+        <v>17.4791185</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08199177986596952</v>
+        <v>0.08243676076596096</v>
       </c>
       <c r="T26">
-        <v>0.7254157296043444</v>
+        <v>0.7343347754601356</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.165148806248254</v>
+        <v>3.038542853998324</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07625007057447072</v>
+        <v>0.07816598845080458</v>
       </c>
       <c r="C27">
-        <v>279.8127760102116</v>
+        <v>254.7939661536748</v>
       </c>
       <c r="D27">
-        <v>354.1627760102116</v>
+        <v>333.1979661536748</v>
       </c>
       <c r="E27">
-        <v>47.75</v>
+        <v>51.804</v>
       </c>
       <c r="F27">
-        <v>101.35</v>
+        <v>105.404</v>
       </c>
       <c r="G27">
         <v>27</v>
@@ -3501,45 +3501,45 @@
         <v>19.74</v>
       </c>
       <c r="M27">
-        <v>6.496535000000001</v>
+        <v>7.578547600000001</v>
       </c>
       <c r="N27">
-        <v>13.243465</v>
+        <v>12.1614524</v>
       </c>
       <c r="O27">
-        <v>1.3243465</v>
+        <v>1.21614524</v>
       </c>
       <c r="P27">
-        <v>11.9191185</v>
+        <v>10.94530716</v>
       </c>
       <c r="Q27">
-        <v>17.4791185</v>
+        <v>16.50530716</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08243676076596096</v>
+        <v>0.08289376817676296</v>
       </c>
       <c r="T27">
-        <v>0.7343347754601356</v>
+        <v>0.7434948766093264</v>
       </c>
       <c r="U27">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0.1</v>
       </c>
       <c r="W27">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.038542853998324</v>
+        <v>2.604720725116248</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07816598845080458</v>
+        <v>0.07832690632713847</v>
       </c>
       <c r="C28">
-        <v>254.7939661536748</v>
+        <v>249.0915613354309</v>
       </c>
       <c r="D28">
-        <v>333.1979661536748</v>
+        <v>331.5495613354309</v>
       </c>
       <c r="E28">
-        <v>51.804</v>
+        <v>55.858</v>
       </c>
       <c r="F28">
-        <v>105.404</v>
+        <v>109.458</v>
       </c>
       <c r="G28">
         <v>27</v>
@@ -3583,28 +3583,28 @@
         <v>19.74</v>
       </c>
       <c r="M28">
-        <v>7.578547600000001</v>
+        <v>7.870030200000001</v>
       </c>
       <c r="N28">
-        <v>12.1614524</v>
+        <v>11.8699698</v>
       </c>
       <c r="O28">
-        <v>1.21614524</v>
+        <v>1.18699698</v>
       </c>
       <c r="P28">
-        <v>10.94530716</v>
+        <v>10.68297282</v>
       </c>
       <c r="Q28">
-        <v>16.50530716</v>
+        <v>16.24297282</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08289376817676296</v>
+        <v>0.08336329633854585</v>
       </c>
       <c r="T28">
-        <v>0.7434948766093264</v>
+        <v>0.7529059394338377</v>
       </c>
       <c r="U28">
         <v>0.07190000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.604720725116248</v>
+        <v>2.508249587148979</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07832690632713847</v>
+        <v>0.07947062420347234</v>
       </c>
       <c r="C29">
-        <v>249.0915613354309</v>
+        <v>233.7755438005472</v>
       </c>
       <c r="D29">
-        <v>331.5495613354309</v>
+        <v>320.2875438005472</v>
       </c>
       <c r="E29">
-        <v>55.858</v>
+        <v>59.91200000000001</v>
       </c>
       <c r="F29">
-        <v>109.458</v>
+        <v>113.512</v>
       </c>
       <c r="G29">
         <v>27</v>
@@ -3665,45 +3665,45 @@
         <v>19.74</v>
       </c>
       <c r="M29">
-        <v>7.870030200000001</v>
+        <v>8.604209600000003</v>
       </c>
       <c r="N29">
-        <v>11.8699698</v>
+        <v>11.1357904</v>
       </c>
       <c r="O29">
-        <v>1.18699698</v>
+        <v>1.11357904</v>
       </c>
       <c r="P29">
-        <v>10.68297282</v>
+        <v>10.02221136</v>
       </c>
       <c r="Q29">
-        <v>16.24297282</v>
+        <v>15.58221136</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08336329633854585</v>
+        <v>0.08384586694926714</v>
       </c>
       <c r="T29">
-        <v>0.7529059394338377</v>
+        <v>0.7625784206701408</v>
       </c>
       <c r="U29">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0.1</v>
       </c>
       <c r="W29">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.508249587148979</v>
+        <v>2.294225840337501</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07947062420347234</v>
+        <v>0.07966664207980623</v>
       </c>
       <c r="C30">
-        <v>233.7755438005472</v>
+        <v>227.8677407573038</v>
       </c>
       <c r="D30">
-        <v>320.2875438005472</v>
+        <v>318.4337407573038</v>
       </c>
       <c r="E30">
-        <v>59.91200000000001</v>
+        <v>63.96600000000002</v>
       </c>
       <c r="F30">
-        <v>113.512</v>
+        <v>117.566</v>
       </c>
       <c r="G30">
         <v>27</v>
@@ -3747,28 +3747,28 @@
         <v>19.74</v>
       </c>
       <c r="M30">
-        <v>8.604209600000003</v>
+        <v>8.911502800000003</v>
       </c>
       <c r="N30">
-        <v>11.1357904</v>
+        <v>10.8284972</v>
       </c>
       <c r="O30">
-        <v>1.11357904</v>
+        <v>1.08284972</v>
       </c>
       <c r="P30">
-        <v>10.02221136</v>
+        <v>9.745647479999999</v>
       </c>
       <c r="Q30">
-        <v>15.58221136</v>
+        <v>15.30564748</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08384586694926714</v>
+        <v>0.08434203109831862</v>
       </c>
       <c r="T30">
-        <v>0.7625784206701408</v>
+        <v>0.7725233661666215</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.294225840337501</v>
+        <v>2.215114604463794</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07966664207980621</v>
+        <v>0.07986265995614009</v>
       </c>
       <c r="C31">
-        <v>227.8677407573039</v>
+        <v>221.9812736012842</v>
       </c>
       <c r="D31">
-        <v>318.433740757304</v>
+        <v>316.6012736012842</v>
       </c>
       <c r="E31">
-        <v>63.96599999999999</v>
+        <v>68.02</v>
       </c>
       <c r="F31">
-        <v>117.566</v>
+        <v>121.62</v>
       </c>
       <c r="G31">
         <v>27</v>
@@ -3829,28 +3829,28 @@
         <v>19.74</v>
       </c>
       <c r="M31">
-        <v>8.911502800000001</v>
+        <v>9.218796000000001</v>
       </c>
       <c r="N31">
-        <v>10.8284972</v>
+        <v>10.521204</v>
       </c>
       <c r="O31">
-        <v>1.08284972</v>
+        <v>1.0521204</v>
       </c>
       <c r="P31">
-        <v>9.745647480000001</v>
+        <v>9.469083600000001</v>
       </c>
       <c r="Q31">
-        <v>15.30564748</v>
+        <v>15.0290836</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08434203109831862</v>
+        <v>0.08485237136591442</v>
       </c>
       <c r="T31">
-        <v>0.7725233661666214</v>
+        <v>0.7827524529630017</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.215114604463795</v>
+        <v>2.141277450981669</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07986265995614009</v>
+        <v>0.08005867783247397</v>
       </c>
       <c r="C32">
-        <v>221.9812736012842</v>
+        <v>216.115776099851</v>
       </c>
       <c r="D32">
-        <v>316.6012736012842</v>
+        <v>314.7897760998511</v>
       </c>
       <c r="E32">
-        <v>68.02</v>
+        <v>72.074</v>
       </c>
       <c r="F32">
-        <v>121.62</v>
+        <v>125.674</v>
       </c>
       <c r="G32">
         <v>27</v>
@@ -3911,28 +3911,28 @@
         <v>19.74</v>
       </c>
       <c r="M32">
-        <v>9.218796000000001</v>
+        <v>9.526089200000001</v>
       </c>
       <c r="N32">
-        <v>10.521204</v>
+        <v>10.2139108</v>
       </c>
       <c r="O32">
-        <v>1.0521204</v>
+        <v>1.02139108</v>
       </c>
       <c r="P32">
-        <v>9.469083600000001</v>
+        <v>9.19251972</v>
       </c>
       <c r="Q32">
-        <v>15.0290836</v>
+        <v>14.75251972</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08485237136591442</v>
+        <v>0.08537750410503475</v>
       </c>
       <c r="T32">
-        <v>0.7827524529630017</v>
+        <v>0.7932780350288422</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.141277450981669</v>
+        <v>2.072203984820969</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08005867783247397</v>
+        <v>0.08025469570880783</v>
       </c>
       <c r="C33">
-        <v>216.115776099851</v>
+        <v>210.2708903545757</v>
       </c>
       <c r="D33">
-        <v>314.7897760998511</v>
+        <v>312.9988903545757</v>
       </c>
       <c r="E33">
-        <v>72.074</v>
+        <v>76.128</v>
       </c>
       <c r="F33">
-        <v>125.674</v>
+        <v>129.728</v>
       </c>
       <c r="G33">
         <v>27</v>
@@ -3993,28 +3993,28 @@
         <v>19.74</v>
       </c>
       <c r="M33">
-        <v>9.526089200000001</v>
+        <v>9.833382400000001</v>
       </c>
       <c r="N33">
-        <v>10.2139108</v>
+        <v>9.906617600000001</v>
       </c>
       <c r="O33">
-        <v>1.02139108</v>
+        <v>0.9906617600000001</v>
       </c>
       <c r="P33">
-        <v>9.19251972</v>
+        <v>8.915955840000001</v>
       </c>
       <c r="Q33">
-        <v>14.75251972</v>
+        <v>14.47595584</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08537750410503475</v>
+        <v>0.08591808192471742</v>
       </c>
       <c r="T33">
-        <v>0.7932780350288422</v>
+        <v>0.8041131930377955</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.072203984820969</v>
+        <v>2.007447610295314</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08025469570880783</v>
+        <v>0.08466811358514172</v>
       </c>
       <c r="C34">
-        <v>210.2708903545757</v>
+        <v>170.6763207064612</v>
       </c>
       <c r="D34">
-        <v>312.9988903545757</v>
+        <v>277.4583207064612</v>
       </c>
       <c r="E34">
-        <v>76.128</v>
+        <v>80.182</v>
       </c>
       <c r="F34">
-        <v>129.728</v>
+        <v>133.782</v>
       </c>
       <c r="G34">
         <v>27</v>
@@ -4075,45 +4075,45 @@
         <v>19.74</v>
       </c>
       <c r="M34">
-        <v>9.833382400000001</v>
+        <v>12.04038</v>
       </c>
       <c r="N34">
-        <v>9.906617600000001</v>
+        <v>7.699620000000001</v>
       </c>
       <c r="O34">
-        <v>0.9906617600000001</v>
+        <v>0.7699620000000001</v>
       </c>
       <c r="P34">
-        <v>8.915955840000001</v>
+        <v>6.929658000000001</v>
       </c>
       <c r="Q34">
-        <v>14.47595584</v>
+        <v>12.489658</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08591808192471742</v>
+        <v>0.08647479639573391</v>
       </c>
       <c r="T34">
-        <v>0.8041131930377955</v>
+        <v>0.815271788599255</v>
       </c>
       <c r="U34">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V34">
         <v>0.1</v>
       </c>
       <c r="W34">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.007447610295314</v>
+        <v>1.639483139236469</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08466811358514172</v>
+        <v>0.0849919314614756</v>
       </c>
       <c r="C35">
-        <v>170.6763207064612</v>
+        <v>164.3298599669172</v>
       </c>
       <c r="D35">
-        <v>277.4583207064612</v>
+        <v>275.1658599669172</v>
       </c>
       <c r="E35">
-        <v>80.182</v>
+        <v>84.236</v>
       </c>
       <c r="F35">
-        <v>133.782</v>
+        <v>137.836</v>
       </c>
       <c r="G35">
         <v>27</v>
@@ -4157,28 +4157,28 @@
         <v>19.74</v>
       </c>
       <c r="M35">
-        <v>12.04038</v>
+        <v>12.40524</v>
       </c>
       <c r="N35">
-        <v>7.699620000000001</v>
+        <v>7.334760000000001</v>
       </c>
       <c r="O35">
-        <v>0.7699620000000001</v>
+        <v>0.7334760000000001</v>
       </c>
       <c r="P35">
-        <v>6.929658000000001</v>
+        <v>6.601284000000001</v>
       </c>
       <c r="Q35">
-        <v>12.489658</v>
+        <v>12.161284</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08647479639573391</v>
+        <v>0.08704838100223576</v>
       </c>
       <c r="T35">
-        <v>0.815271788599255</v>
+        <v>0.8267685234201527</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.639483139236469</v>
+        <v>1.591263046905985</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0849919314614756</v>
+        <v>0.08531574933780947</v>
       </c>
       <c r="C36">
-        <v>164.3298599669172</v>
+        <v>158.0209710705344</v>
       </c>
       <c r="D36">
-        <v>275.1658599669172</v>
+        <v>272.9109710705345</v>
       </c>
       <c r="E36">
-        <v>84.236</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="F36">
-        <v>137.836</v>
+        <v>141.89</v>
       </c>
       <c r="G36">
         <v>27</v>
@@ -4239,28 +4239,28 @@
         <v>19.74</v>
       </c>
       <c r="M36">
-        <v>12.40524</v>
+        <v>12.7701</v>
       </c>
       <c r="N36">
-        <v>7.334760000000001</v>
+        <v>6.969900000000001</v>
       </c>
       <c r="O36">
-        <v>0.7334760000000001</v>
+        <v>0.6969900000000001</v>
       </c>
       <c r="P36">
-        <v>6.601284000000001</v>
+        <v>6.27291</v>
       </c>
       <c r="Q36">
-        <v>12.161284</v>
+        <v>11.83291</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08704838100223576</v>
+        <v>0.08763961436586074</v>
       </c>
       <c r="T36">
-        <v>0.8267685234201527</v>
+        <v>0.8386190039278472</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.591263046905985</v>
+        <v>1.545798388422957</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08531574933780947</v>
+        <v>0.08563956721414334</v>
       </c>
       <c r="C37">
-        <v>158.0209710705344</v>
+        <v>151.7487378601872</v>
       </c>
       <c r="D37">
-        <v>272.9109710705345</v>
+        <v>270.6927378601872</v>
       </c>
       <c r="E37">
-        <v>88.29000000000001</v>
+        <v>92.34400000000001</v>
       </c>
       <c r="F37">
-        <v>141.89</v>
+        <v>145.944</v>
       </c>
       <c r="G37">
         <v>27</v>
@@ -4321,28 +4321,28 @@
         <v>19.74</v>
       </c>
       <c r="M37">
-        <v>12.7701</v>
+        <v>13.13496</v>
       </c>
       <c r="N37">
-        <v>6.969900000000001</v>
+        <v>6.605040000000001</v>
       </c>
       <c r="O37">
-        <v>0.6969900000000001</v>
+        <v>0.6605040000000001</v>
       </c>
       <c r="P37">
-        <v>6.27291</v>
+        <v>5.944536</v>
       </c>
       <c r="Q37">
-        <v>11.83291</v>
+        <v>11.504536</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08763961436586074</v>
+        <v>0.08824932377209899</v>
       </c>
       <c r="T37">
-        <v>0.8386190039278472</v>
+        <v>0.8508398119514071</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.545798388422957</v>
+        <v>1.502859544300097</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08563956721414334</v>
+        <v>0.1055480751851112</v>
       </c>
       <c r="C38">
-        <v>151.7487378601872</v>
+        <v>57.497881933428</v>
       </c>
       <c r="D38">
-        <v>270.6927378601872</v>
+        <v>180.495881933428</v>
       </c>
       <c r="E38">
-        <v>92.34400000000001</v>
+        <v>96.39800000000001</v>
       </c>
       <c r="F38">
-        <v>145.944</v>
+        <v>149.998</v>
       </c>
       <c r="G38">
         <v>27</v>
@@ -4403,45 +4403,45 @@
         <v>19.74</v>
       </c>
       <c r="M38">
-        <v>13.13496</v>
+        <v>22.0197064</v>
       </c>
       <c r="N38">
-        <v>6.605040000000001</v>
+        <v>-2.279706400000002</v>
       </c>
       <c r="O38">
-        <v>0.6605040000000001</v>
+        <v>-0.2279706400000002</v>
       </c>
       <c r="P38">
-        <v>5.944536</v>
+        <v>-2.051735760000002</v>
       </c>
       <c r="Q38">
-        <v>11.504536</v>
+        <v>3.508264239999998</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08824932377209899</v>
+        <v>0.08904974620419606</v>
       </c>
       <c r="T38">
-        <v>0.8508398119514071</v>
+        <v>0.8668832070185104</v>
       </c>
       <c r="U38">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1</v>
+        <v>0.08964697185971562</v>
       </c>
       <c r="W38">
-        <v>0.081</v>
+        <v>0.1336398245309938</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>1.502859544300097</v>
+        <v>0.8964697185971562</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1055480751851112</v>
+        <v>0.1065580751851112</v>
       </c>
       <c r="C39">
-        <v>57.497881933428</v>
+        <v>50.44344388141025</v>
       </c>
       <c r="D39">
-        <v>180.495881933428</v>
+        <v>177.4954438814103</v>
       </c>
       <c r="E39">
-        <v>96.39800000000001</v>
+        <v>100.452</v>
       </c>
       <c r="F39">
-        <v>149.998</v>
+        <v>154.052</v>
       </c>
       <c r="G39">
         <v>27</v>
@@ -4485,37 +4485,37 @@
         <v>19.74</v>
       </c>
       <c r="M39">
-        <v>22.0197064</v>
+        <v>22.6148336</v>
       </c>
       <c r="N39">
-        <v>-2.279706400000002</v>
+        <v>-2.874833600000002</v>
       </c>
       <c r="O39">
-        <v>-0.2279706400000002</v>
+        <v>-0.2874833600000002</v>
       </c>
       <c r="P39">
-        <v>-2.051735760000002</v>
+        <v>-2.587350240000002</v>
       </c>
       <c r="Q39">
-        <v>3.508264239999998</v>
+        <v>2.972649759999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08904974620419606</v>
+        <v>0.08974732275587664</v>
       </c>
       <c r="T39">
-        <v>0.8668832070185104</v>
+        <v>0.8808651942284863</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.08964697185971562</v>
+        <v>0.08728784102130205</v>
       </c>
       <c r="W39">
-        <v>0.1336398245309938</v>
+        <v>0.1339861449380729</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8964697185971562</v>
+        <v>0.8728784102130205</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1065580751851112</v>
+        <v>0.1075680751851112</v>
       </c>
       <c r="C40">
-        <v>50.44344388141025</v>
+        <v>43.48712908880947</v>
       </c>
       <c r="D40">
-        <v>177.4954438814103</v>
+        <v>174.5931290888095</v>
       </c>
       <c r="E40">
-        <v>100.452</v>
+        <v>104.506</v>
       </c>
       <c r="F40">
-        <v>154.052</v>
+        <v>158.106</v>
       </c>
       <c r="G40">
         <v>27</v>
@@ -4567,37 +4567,37 @@
         <v>19.74</v>
       </c>
       <c r="M40">
-        <v>22.6148336</v>
+        <v>23.2099608</v>
       </c>
       <c r="N40">
-        <v>-2.874833600000002</v>
+        <v>-3.469960800000003</v>
       </c>
       <c r="O40">
-        <v>-0.2874833600000002</v>
+        <v>-0.3469960800000003</v>
       </c>
       <c r="P40">
-        <v>-2.587350240000002</v>
+        <v>-3.122964720000002</v>
       </c>
       <c r="Q40">
-        <v>2.972649759999998</v>
+        <v>2.437035279999997</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08974732275587664</v>
+        <v>0.09046777066990741</v>
       </c>
       <c r="T40">
-        <v>0.8808651942284863</v>
+        <v>0.8953056072486255</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.08728784102130205</v>
+        <v>0.08504969125152508</v>
       </c>
       <c r="W40">
-        <v>0.1339861449380729</v>
+        <v>0.1343147053242761</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8728784102130205</v>
+        <v>0.8504969125152507</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1075680751851112</v>
+        <v>0.1085780751851112</v>
       </c>
       <c r="C41">
-        <v>43.48712908880947</v>
+        <v>36.6242016111872</v>
       </c>
       <c r="D41">
-        <v>174.5931290888095</v>
+        <v>171.7842016111872</v>
       </c>
       <c r="E41">
-        <v>104.506</v>
+        <v>108.56</v>
       </c>
       <c r="F41">
-        <v>158.106</v>
+        <v>162.16</v>
       </c>
       <c r="G41">
         <v>27</v>
@@ -4649,37 +4649,37 @@
         <v>19.74</v>
       </c>
       <c r="M41">
-        <v>23.2099608</v>
+        <v>23.805088</v>
       </c>
       <c r="N41">
-        <v>-3.469960800000003</v>
+        <v>-4.065088000000003</v>
       </c>
       <c r="O41">
-        <v>-0.3469960800000003</v>
+        <v>-0.4065088000000003</v>
       </c>
       <c r="P41">
-        <v>-3.122964720000002</v>
+        <v>-3.658579200000003</v>
       </c>
       <c r="Q41">
-        <v>2.437035279999997</v>
+        <v>1.901420799999997</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09046777066990741</v>
+        <v>0.09121223351440587</v>
       </c>
       <c r="T41">
-        <v>0.8953056072486255</v>
+        <v>0.910227367369436</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.08504969125152508</v>
+        <v>0.08292344897023696</v>
       </c>
       <c r="W41">
-        <v>0.1343147053242761</v>
+        <v>0.1346268376911692</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8504969125152507</v>
+        <v>0.8292344897023695</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1085780751851112</v>
+        <v>0.1095880751851112</v>
       </c>
       <c r="C42">
-        <v>36.6242016111872</v>
+        <v>29.85022545382859</v>
       </c>
       <c r="D42">
-        <v>171.7842016111872</v>
+        <v>169.0642254538286</v>
       </c>
       <c r="E42">
-        <v>108.56</v>
+        <v>112.614</v>
       </c>
       <c r="F42">
-        <v>162.16</v>
+        <v>166.214</v>
       </c>
       <c r="G42">
         <v>27</v>
@@ -4731,37 +4731,37 @@
         <v>19.74</v>
       </c>
       <c r="M42">
-        <v>23.805088</v>
+        <v>24.40021520000001</v>
       </c>
       <c r="N42">
-        <v>-4.065088000000003</v>
+        <v>-4.660215200000003</v>
       </c>
       <c r="O42">
-        <v>-0.4065088000000003</v>
+        <v>-0.4660215200000004</v>
       </c>
       <c r="P42">
-        <v>-3.658579200000003</v>
+        <v>-4.194193680000003</v>
       </c>
       <c r="Q42">
-        <v>1.901420799999997</v>
+        <v>1.365806319999996</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09121223351440587</v>
+        <v>0.09198193238753138</v>
       </c>
       <c r="T42">
-        <v>0.910227367369436</v>
+        <v>0.925654949867223</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.08292344897023696</v>
+        <v>0.08090092582462141</v>
       </c>
       <c r="W42">
-        <v>0.1346268376911692</v>
+        <v>0.1349237440889456</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8292344897023695</v>
+        <v>0.8090092582462141</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1095880751851112</v>
+        <v>0.1335294612015651</v>
       </c>
       <c r="C43">
-        <v>29.85022545382859</v>
+        <v>-20.34143261138115</v>
       </c>
       <c r="D43">
-        <v>169.0642254538286</v>
+        <v>122.9265673886189</v>
       </c>
       <c r="E43">
-        <v>112.614</v>
+        <v>116.668</v>
       </c>
       <c r="F43">
-        <v>166.214</v>
+        <v>170.268</v>
       </c>
       <c r="G43">
         <v>27</v>
@@ -4813,45 +4813,45 @@
         <v>19.74</v>
       </c>
       <c r="M43">
-        <v>24.40021520000001</v>
+        <v>34.18981440000001</v>
       </c>
       <c r="N43">
-        <v>-4.660215200000003</v>
+        <v>-14.44981440000001</v>
       </c>
       <c r="O43">
-        <v>-0.4660215200000004</v>
+        <v>-1.444981440000001</v>
       </c>
       <c r="P43">
-        <v>-4.194193680000003</v>
+        <v>-13.00483296000001</v>
       </c>
       <c r="Q43">
-        <v>1.365806319999996</v>
+        <v>-7.444832960000007</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09198193238753138</v>
+        <v>0.09321159676740928</v>
       </c>
       <c r="T43">
-        <v>0.925654949867223</v>
+        <v>0.95030192458361</v>
       </c>
       <c r="U43">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.08090092582462141</v>
+        <v>0.05773649359149489</v>
       </c>
       <c r="W43">
-        <v>0.1349237440889456</v>
+        <v>0.1892065120868278</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.8090092582462141</v>
+        <v>0.5773649359149489</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1335294612015651</v>
+        <v>0.1350794612015651</v>
       </c>
       <c r="C44">
-        <v>-20.34143261138112</v>
+        <v>-26.52958728579378</v>
       </c>
       <c r="D44">
-        <v>122.9265673886189</v>
+        <v>120.7924127142062</v>
       </c>
       <c r="E44">
-        <v>116.668</v>
+        <v>120.722</v>
       </c>
       <c r="F44">
-        <v>170.268</v>
+        <v>174.322</v>
       </c>
       <c r="G44">
         <v>27</v>
@@ -4895,37 +4895,37 @@
         <v>19.74</v>
       </c>
       <c r="M44">
-        <v>34.1898144</v>
+        <v>35.0038576</v>
       </c>
       <c r="N44">
-        <v>-14.4498144</v>
+        <v>-15.2638576</v>
       </c>
       <c r="O44">
-        <v>-1.44498144</v>
+        <v>-1.52638576</v>
       </c>
       <c r="P44">
-        <v>-13.00483296</v>
+        <v>-13.73747184</v>
       </c>
       <c r="Q44">
-        <v>-7.444832960000002</v>
+        <v>-8.177471840000003</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09321159676740928</v>
+        <v>0.09404337916683751</v>
       </c>
       <c r="T44">
-        <v>0.9503019245836098</v>
+        <v>0.9669738881727961</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.0577364935914949</v>
+        <v>0.05639378443820432</v>
       </c>
       <c r="W44">
-        <v>0.1892065120868278</v>
+        <v>0.1894761280848086</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.577364935914949</v>
+        <v>0.5639378443820432</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1350794612015651</v>
+        <v>0.1366294612015651</v>
       </c>
       <c r="C45">
-        <v>-26.52958728579378</v>
+        <v>-32.64490348463735</v>
       </c>
       <c r="D45">
-        <v>120.7924127142062</v>
+        <v>118.7310965153627</v>
       </c>
       <c r="E45">
-        <v>120.722</v>
+        <v>124.776</v>
       </c>
       <c r="F45">
-        <v>174.322</v>
+        <v>178.376</v>
       </c>
       <c r="G45">
         <v>27</v>
@@ -4977,37 +4977,37 @@
         <v>19.74</v>
       </c>
       <c r="M45">
-        <v>35.0038576</v>
+        <v>35.8179008</v>
       </c>
       <c r="N45">
-        <v>-15.2638576</v>
+        <v>-16.0779008</v>
       </c>
       <c r="O45">
-        <v>-1.52638576</v>
+        <v>-1.60779008</v>
       </c>
       <c r="P45">
-        <v>-13.73747184</v>
+        <v>-14.47011072</v>
       </c>
       <c r="Q45">
-        <v>-8.177471840000003</v>
+        <v>-8.910110720000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09404337916683751</v>
+        <v>0.09490486808053103</v>
       </c>
       <c r="T45">
-        <v>0.9669738881727961</v>
+        <v>0.9842412790330245</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.05639378443820432</v>
+        <v>0.05511210751915422</v>
       </c>
       <c r="W45">
-        <v>0.1894761280848086</v>
+        <v>0.1897334888101538</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5639378443820432</v>
+        <v>0.5511210751915422</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1366294612015651</v>
+        <v>0.1381794612015651</v>
       </c>
       <c r="C46">
-        <v>-32.64490348463735</v>
+        <v>-38.69104759551567</v>
       </c>
       <c r="D46">
-        <v>118.7310965153627</v>
+        <v>116.7389524044843</v>
       </c>
       <c r="E46">
-        <v>124.776</v>
+        <v>128.83</v>
       </c>
       <c r="F46">
-        <v>178.376</v>
+        <v>182.43</v>
       </c>
       <c r="G46">
         <v>27</v>
@@ -5059,37 +5059,37 @@
         <v>19.74</v>
       </c>
       <c r="M46">
-        <v>35.8179008</v>
+        <v>36.631944</v>
       </c>
       <c r="N46">
-        <v>-16.0779008</v>
+        <v>-16.891944</v>
       </c>
       <c r="O46">
-        <v>-1.60779008</v>
+        <v>-1.6891944</v>
       </c>
       <c r="P46">
-        <v>-14.47011072</v>
+        <v>-15.2027496</v>
       </c>
       <c r="Q46">
-        <v>-8.910110720000002</v>
+        <v>-9.642749600000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09490486808053103</v>
+        <v>0.0957976838638134</v>
       </c>
       <c r="T46">
-        <v>0.9842412790330245</v>
+        <v>1.002136575015443</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.05511210751915422</v>
+        <v>0.05388739401872858</v>
       </c>
       <c r="W46">
-        <v>0.1897334888101538</v>
+        <v>0.1899794112810393</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5511210751915422</v>
+        <v>0.5388739401872857</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1381794612015651</v>
+        <v>0.1397294612015651</v>
       </c>
       <c r="C47">
-        <v>-38.69104759551567</v>
+        <v>-44.671443998862</v>
       </c>
       <c r="D47">
-        <v>116.7389524044843</v>
+        <v>114.812556001138</v>
       </c>
       <c r="E47">
-        <v>128.83</v>
+        <v>132.884</v>
       </c>
       <c r="F47">
-        <v>182.43</v>
+        <v>186.484</v>
       </c>
       <c r="G47">
         <v>27</v>
@@ -5141,37 +5141,37 @@
         <v>19.74</v>
       </c>
       <c r="M47">
-        <v>36.631944</v>
+        <v>37.44598720000001</v>
       </c>
       <c r="N47">
-        <v>-16.891944</v>
+        <v>-17.70598720000001</v>
       </c>
       <c r="O47">
-        <v>-1.6891944</v>
+        <v>-1.770598720000001</v>
       </c>
       <c r="P47">
-        <v>-15.2027496</v>
+        <v>-15.93538848000001</v>
       </c>
       <c r="Q47">
-        <v>-9.642749600000002</v>
+        <v>-10.37538848000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0957976838638134</v>
+        <v>0.09672356689832848</v>
       </c>
       <c r="T47">
-        <v>1.002136575015443</v>
+        <v>1.020694659737951</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.05388739401872858</v>
+        <v>0.0527159289313649</v>
       </c>
       <c r="W47">
-        <v>0.1899794112810393</v>
+        <v>0.1902146414705819</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5388739401872857</v>
+        <v>0.527159289313649</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1397294612015651</v>
+        <v>0.1412794612015651</v>
       </c>
       <c r="C48">
-        <v>-44.671443998862</v>
+        <v>-50.58929471148889</v>
       </c>
       <c r="D48">
-        <v>114.812556001138</v>
+        <v>112.9487052885111</v>
       </c>
       <c r="E48">
-        <v>132.884</v>
+        <v>136.938</v>
       </c>
       <c r="F48">
-        <v>186.484</v>
+        <v>190.538</v>
       </c>
       <c r="G48">
         <v>27</v>
@@ -5223,37 +5223,37 @@
         <v>19.74</v>
       </c>
       <c r="M48">
-        <v>37.44598720000001</v>
+        <v>38.26003040000001</v>
       </c>
       <c r="N48">
-        <v>-17.70598720000001</v>
+        <v>-18.52003040000001</v>
       </c>
       <c r="O48">
-        <v>-1.770598720000001</v>
+        <v>-1.852003040000001</v>
       </c>
       <c r="P48">
-        <v>-15.93538848000001</v>
+        <v>-16.66802736000001</v>
       </c>
       <c r="Q48">
-        <v>-10.37538848000001</v>
+        <v>-11.10802736000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09672356689832848</v>
+        <v>0.09768438891527809</v>
       </c>
       <c r="T48">
-        <v>1.020694659737951</v>
+        <v>1.039953049544328</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.0527159289313649</v>
+        <v>0.05159431342218693</v>
       </c>
       <c r="W48">
-        <v>0.1902146414705819</v>
+        <v>0.1904398618648249</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.527159289313649</v>
+        <v>0.5159431342218692</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1412794612015651</v>
+        <v>0.1428294612015651</v>
       </c>
       <c r="C49">
-        <v>-50.58929471148889</v>
+        <v>-56.44759714735943</v>
       </c>
       <c r="D49">
-        <v>112.9487052885111</v>
+        <v>111.1444028526406</v>
       </c>
       <c r="E49">
-        <v>136.938</v>
+        <v>140.992</v>
       </c>
       <c r="F49">
-        <v>190.538</v>
+        <v>194.592</v>
       </c>
       <c r="G49">
         <v>27</v>
@@ -5305,37 +5305,37 @@
         <v>19.74</v>
       </c>
       <c r="M49">
-        <v>38.26003040000001</v>
+        <v>39.07407360000001</v>
       </c>
       <c r="N49">
-        <v>-18.52003040000001</v>
+        <v>-19.33407360000001</v>
       </c>
       <c r="O49">
-        <v>-1.852003040000001</v>
+        <v>-1.933407360000001</v>
       </c>
       <c r="P49">
-        <v>-16.66802736000001</v>
+        <v>-17.40066624000001</v>
       </c>
       <c r="Q49">
-        <v>-11.10802736000001</v>
+        <v>-11.84066624000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09768438891527809</v>
+        <v>0.09868216562518727</v>
       </c>
       <c r="T49">
-        <v>1.039953049544328</v>
+        <v>1.059952146650949</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.05159431342218693</v>
+        <v>0.05051943189255802</v>
       </c>
       <c r="W49">
-        <v>0.1904398618648249</v>
+        <v>0.1906556980759744</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5159431342218692</v>
+        <v>0.5051943189255803</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1428294612015651</v>
+        <v>0.1616308984956105</v>
       </c>
       <c r="C50">
-        <v>-56.4475971473594</v>
+        <v>-78.54233194229187</v>
       </c>
       <c r="D50">
-        <v>111.1444028526406</v>
+        <v>93.10366805770815</v>
       </c>
       <c r="E50">
-        <v>140.992</v>
+        <v>145.046</v>
       </c>
       <c r="F50">
-        <v>194.592</v>
+        <v>198.646</v>
       </c>
       <c r="G50">
         <v>27</v>
@@ -5387,45 +5387,45 @@
         <v>19.74</v>
       </c>
       <c r="M50">
-        <v>39.07407360000001</v>
+        <v>46.84072680000001</v>
       </c>
       <c r="N50">
-        <v>-19.3340736</v>
+        <v>-27.1007268</v>
       </c>
       <c r="O50">
-        <v>-1.93340736</v>
+        <v>-2.710072680000001</v>
       </c>
       <c r="P50">
-        <v>-17.40066624</v>
+        <v>-24.39065412</v>
       </c>
       <c r="Q50">
-        <v>-11.84066624</v>
+        <v>-18.83065412000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09868216562518727</v>
+        <v>0.09991796748851542</v>
       </c>
       <c r="T50">
-        <v>1.059952146650949</v>
+        <v>1.084722138998729</v>
       </c>
       <c r="U50">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05051943189255803</v>
+        <v>0.04214281320673274</v>
       </c>
       <c r="W50">
-        <v>0.1906556980759744</v>
+        <v>0.2258627246458524</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.5051943189255803</v>
+        <v>0.4214281320673273</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1616308984956105</v>
+        <v>0.1635308984956106</v>
       </c>
       <c r="C51">
-        <v>-78.54233194229187</v>
+        <v>-84.09888540591166</v>
       </c>
       <c r="D51">
-        <v>93.10366805770815</v>
+        <v>91.60111459408836</v>
       </c>
       <c r="E51">
-        <v>145.046</v>
+        <v>149.1</v>
       </c>
       <c r="F51">
-        <v>198.646</v>
+        <v>202.7</v>
       </c>
       <c r="G51">
         <v>27</v>
@@ -5469,37 +5469,37 @@
         <v>19.74</v>
       </c>
       <c r="M51">
-        <v>46.84072680000001</v>
+        <v>47.79666</v>
       </c>
       <c r="N51">
-        <v>-27.1007268</v>
+        <v>-28.05666</v>
       </c>
       <c r="O51">
-        <v>-2.710072680000001</v>
+        <v>-2.805666</v>
       </c>
       <c r="P51">
-        <v>-24.39065412</v>
+        <v>-25.250994</v>
       </c>
       <c r="Q51">
-        <v>-18.83065412000001</v>
+        <v>-19.690994</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09991796748851542</v>
+        <v>0.1010003268382857</v>
       </c>
       <c r="T51">
-        <v>1.084722138998729</v>
+        <v>1.106416581778704</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04214281320673274</v>
+        <v>0.04129995694259808</v>
       </c>
       <c r="W51">
-        <v>0.2258627246458524</v>
+        <v>0.2260614701529354</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4214281320673273</v>
+        <v>0.4129995694259808</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1635308984956106</v>
+        <v>0.1654308984956106</v>
       </c>
       <c r="C52">
-        <v>-84.09888540591166</v>
+        <v>-89.60771120691616</v>
       </c>
       <c r="D52">
-        <v>91.60111459408836</v>
+        <v>90.14628879308385</v>
       </c>
       <c r="E52">
-        <v>149.1</v>
+        <v>153.154</v>
       </c>
       <c r="F52">
-        <v>202.7</v>
+        <v>206.754</v>
       </c>
       <c r="G52">
         <v>27</v>
@@ -5551,37 +5551,37 @@
         <v>19.74</v>
       </c>
       <c r="M52">
-        <v>47.79666</v>
+        <v>48.75259320000001</v>
       </c>
       <c r="N52">
-        <v>-28.05666</v>
+        <v>-29.0125932</v>
       </c>
       <c r="O52">
-        <v>-2.805666</v>
+        <v>-2.901259320000001</v>
       </c>
       <c r="P52">
-        <v>-25.250994</v>
+        <v>-26.11133388</v>
       </c>
       <c r="Q52">
-        <v>-19.690994</v>
+        <v>-20.55133388</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1010003268382857</v>
+        <v>0.1021268641206997</v>
       </c>
       <c r="T52">
-        <v>1.106416581778704</v>
+        <v>1.128996512019086</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04129995694259808</v>
+        <v>0.04049015386529223</v>
       </c>
       <c r="W52">
-        <v>0.2260614701529354</v>
+        <v>0.2262524217185641</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4129995694259808</v>
+        <v>0.4049015386529223</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1654308984956106</v>
+        <v>0.1673308984956106</v>
       </c>
       <c r="C53">
-        <v>-89.60771120691616</v>
+        <v>-95.07104785156416</v>
       </c>
       <c r="D53">
-        <v>90.14628879308385</v>
+        <v>88.73695214843586</v>
       </c>
       <c r="E53">
-        <v>153.154</v>
+        <v>157.208</v>
       </c>
       <c r="F53">
-        <v>206.754</v>
+        <v>210.808</v>
       </c>
       <c r="G53">
         <v>27</v>
@@ -5633,37 +5633,37 @@
         <v>19.74</v>
       </c>
       <c r="M53">
-        <v>48.75259320000001</v>
+        <v>49.7085264</v>
       </c>
       <c r="N53">
-        <v>-29.0125932</v>
+        <v>-29.9685264</v>
       </c>
       <c r="O53">
-        <v>-2.901259320000001</v>
+        <v>-2.99685264</v>
       </c>
       <c r="P53">
-        <v>-26.11133388</v>
+        <v>-26.97167376</v>
       </c>
       <c r="Q53">
-        <v>-20.55133388</v>
+        <v>-21.41167376</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1021268641206997</v>
+        <v>0.1033003404565477</v>
       </c>
       <c r="T53">
-        <v>1.128996512019086</v>
+        <v>1.15251727268615</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04049015386529223</v>
+        <v>0.03971149706019047</v>
       </c>
       <c r="W53">
-        <v>0.2262524217185641</v>
+        <v>0.2264360289932071</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4049015386529223</v>
+        <v>0.3971149706019046</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1673308984956106</v>
+        <v>0.1692308984956105</v>
       </c>
       <c r="C54">
-        <v>-95.07104785156416</v>
+        <v>-100.4909960147627</v>
       </c>
       <c r="D54">
-        <v>88.73695214843586</v>
+        <v>87.37100398523729</v>
       </c>
       <c r="E54">
-        <v>157.208</v>
+        <v>161.262</v>
       </c>
       <c r="F54">
-        <v>210.808</v>
+        <v>214.862</v>
       </c>
       <c r="G54">
         <v>27</v>
@@ -5715,37 +5715,37 @@
         <v>19.74</v>
       </c>
       <c r="M54">
-        <v>49.7085264</v>
+        <v>50.66445960000001</v>
       </c>
       <c r="N54">
-        <v>-29.9685264</v>
+        <v>-30.92445960000001</v>
       </c>
       <c r="O54">
-        <v>-2.99685264</v>
+        <v>-3.092445960000001</v>
       </c>
       <c r="P54">
-        <v>-26.97167376</v>
+        <v>-27.83201364000001</v>
       </c>
       <c r="Q54">
-        <v>-21.41167376</v>
+        <v>-22.27201364000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1033003404565477</v>
+        <v>0.1045237519556231</v>
       </c>
       <c r="T54">
-        <v>1.15251727268615</v>
+        <v>1.177038916785855</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03971149706019047</v>
+        <v>0.0389622235307529</v>
       </c>
       <c r="W54">
-        <v>0.2264360289932071</v>
+        <v>0.2266127076914485</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3971149706019046</v>
+        <v>0.389622235307529</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1692308984956105</v>
+        <v>0.1711308984956106</v>
       </c>
       <c r="C55">
-        <v>-100.4909960147627</v>
+        <v>-105.8695289875936</v>
       </c>
       <c r="D55">
-        <v>87.37100398523729</v>
+        <v>86.04647101240644</v>
       </c>
       <c r="E55">
-        <v>161.262</v>
+        <v>165.316</v>
       </c>
       <c r="F55">
-        <v>214.862</v>
+        <v>218.916</v>
       </c>
       <c r="G55">
         <v>27</v>
@@ -5797,37 +5797,37 @@
         <v>19.74</v>
       </c>
       <c r="M55">
-        <v>50.66445960000001</v>
+        <v>51.6203928</v>
       </c>
       <c r="N55">
-        <v>-30.92445960000001</v>
+        <v>-31.8803928</v>
       </c>
       <c r="O55">
-        <v>-3.092445960000001</v>
+        <v>-3.18803928</v>
       </c>
       <c r="P55">
-        <v>-27.83201364000001</v>
+        <v>-28.69235352</v>
       </c>
       <c r="Q55">
-        <v>-22.27201364000001</v>
+        <v>-23.13235352</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1045237519556231</v>
+        <v>0.1058003552590062</v>
       </c>
       <c r="T55">
-        <v>1.177038916785855</v>
+        <v>1.202626719324678</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0389622235307529</v>
+        <v>0.03824070087277601</v>
       </c>
       <c r="W55">
-        <v>0.2266127076914485</v>
+        <v>0.2267828427341994</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.389622235307529</v>
+        <v>0.38240700872776</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1711308984956106</v>
+        <v>0.1730308984956105</v>
       </c>
       <c r="C56">
-        <v>-105.8695289875936</v>
+        <v>-111.2085021887316</v>
       </c>
       <c r="D56">
-        <v>86.04647101240644</v>
+        <v>84.76149781126844</v>
       </c>
       <c r="E56">
-        <v>165.316</v>
+        <v>169.37</v>
       </c>
       <c r="F56">
-        <v>218.916</v>
+        <v>222.97</v>
       </c>
       <c r="G56">
         <v>27</v>
@@ -5879,37 +5879,37 @@
         <v>19.74</v>
       </c>
       <c r="M56">
-        <v>51.6203928</v>
+        <v>52.57632600000001</v>
       </c>
       <c r="N56">
-        <v>-31.8803928</v>
+        <v>-32.83632600000001</v>
       </c>
       <c r="O56">
-        <v>-3.18803928</v>
+        <v>-3.283632600000001</v>
       </c>
       <c r="P56">
-        <v>-28.69235352</v>
+        <v>-29.55269340000001</v>
       </c>
       <c r="Q56">
-        <v>-23.13235352</v>
+        <v>-23.99269340000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1058003552590062</v>
+        <v>0.1071336964869841</v>
       </c>
       <c r="T56">
-        <v>1.202626719324678</v>
+        <v>1.229351757531893</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03824070087277601</v>
+        <v>0.03754541540236189</v>
       </c>
       <c r="W56">
-        <v>0.2267828427341994</v>
+        <v>0.2269467910481231</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.38240700872776</v>
+        <v>0.3754541540236189</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1730308984956105</v>
+        <v>0.1749308984956106</v>
       </c>
       <c r="C57">
-        <v>-111.2085021887316</v>
+        <v>-116.5096618361717</v>
       </c>
       <c r="D57">
-        <v>84.76149781126844</v>
+        <v>83.51433816382833</v>
       </c>
       <c r="E57">
-        <v>169.37</v>
+        <v>173.424</v>
       </c>
       <c r="F57">
-        <v>222.97</v>
+        <v>227.024</v>
       </c>
       <c r="G57">
         <v>27</v>
@@ -5961,37 +5961,37 @@
         <v>19.74</v>
       </c>
       <c r="M57">
-        <v>52.57632600000001</v>
+        <v>53.53225920000001</v>
       </c>
       <c r="N57">
-        <v>-32.83632600000001</v>
+        <v>-33.7922592</v>
       </c>
       <c r="O57">
-        <v>-3.283632600000001</v>
+        <v>-3.379225920000001</v>
       </c>
       <c r="P57">
-        <v>-29.55269340000001</v>
+        <v>-30.41303328</v>
       </c>
       <c r="Q57">
-        <v>-23.99269340000001</v>
+        <v>-24.85303328000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1071336964869841</v>
+        <v>0.1085276441344156</v>
       </c>
       <c r="T57">
-        <v>1.229351757531893</v>
+        <v>1.257291570203073</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03754541540236189</v>
+        <v>0.03687496155589114</v>
       </c>
       <c r="W57">
-        <v>0.2269467910481231</v>
+        <v>0.2271048840651209</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3754541540236189</v>
+        <v>0.3687496155589114</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1749308984956106</v>
+        <v>0.1768308984956106</v>
       </c>
       <c r="C58">
-        <v>-116.5096618361717</v>
+        <v>-121.7746528644946</v>
       </c>
       <c r="D58">
-        <v>83.51433816382833</v>
+        <v>82.30334713550542</v>
       </c>
       <c r="E58">
-        <v>173.424</v>
+        <v>177.478</v>
       </c>
       <c r="F58">
-        <v>227.024</v>
+        <v>231.078</v>
       </c>
       <c r="G58">
         <v>27</v>
@@ -6043,37 +6043,37 @@
         <v>19.74</v>
       </c>
       <c r="M58">
-        <v>53.53225920000001</v>
+        <v>54.48819240000001</v>
       </c>
       <c r="N58">
-        <v>-33.7922592</v>
+        <v>-34.74819240000001</v>
       </c>
       <c r="O58">
-        <v>-3.379225920000001</v>
+        <v>-3.474819240000001</v>
       </c>
       <c r="P58">
-        <v>-30.41303328</v>
+        <v>-31.27337316000001</v>
       </c>
       <c r="Q58">
-        <v>-24.85303328000001</v>
+        <v>-25.71337316000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1085276441344156</v>
+        <v>0.1099864265561462</v>
       </c>
       <c r="T58">
-        <v>1.257291570203073</v>
+        <v>1.286530909045005</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03687496155589114</v>
+        <v>0.03622803240578779</v>
       </c>
       <c r="W58">
-        <v>0.2271048840651209</v>
+        <v>0.2272574299587153</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3687496155589114</v>
+        <v>0.3622803240578779</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1768308984956106</v>
+        <v>0.1787308984956106</v>
       </c>
       <c r="C59">
-        <v>-121.7746528644946</v>
+        <v>-127.0050261631572</v>
       </c>
       <c r="D59">
-        <v>82.30334713550542</v>
+        <v>81.12697383684286</v>
       </c>
       <c r="E59">
-        <v>177.478</v>
+        <v>181.532</v>
       </c>
       <c r="F59">
-        <v>231.078</v>
+        <v>235.1320000000001</v>
       </c>
       <c r="G59">
         <v>27</v>
@@ -6125,37 +6125,37 @@
         <v>19.74</v>
       </c>
       <c r="M59">
-        <v>54.48819240000001</v>
+        <v>55.44412560000001</v>
       </c>
       <c r="N59">
-        <v>-34.74819240000001</v>
+        <v>-35.70412560000001</v>
       </c>
       <c r="O59">
-        <v>-3.474819240000001</v>
+        <v>-3.570412560000001</v>
       </c>
       <c r="P59">
-        <v>-31.27337316000001</v>
+        <v>-32.13371304000001</v>
       </c>
       <c r="Q59">
-        <v>-25.71337316000001</v>
+        <v>-26.57371304000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1099864265561462</v>
+        <v>0.111514674807483</v>
       </c>
       <c r="T59">
-        <v>1.286530909045005</v>
+        <v>1.3171625973556</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03622803240578779</v>
+        <v>0.03560341115741213</v>
       </c>
       <c r="W59">
-        <v>0.2272574299587153</v>
+        <v>0.2274047156490822</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3622803240578779</v>
+        <v>0.3560341115741213</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1787308984956106</v>
+        <v>0.1806308984956105</v>
       </c>
       <c r="C60">
-        <v>-127.0050261631571</v>
+        <v>-132.2022452027827</v>
       </c>
       <c r="D60">
-        <v>81.12697383684286</v>
+        <v>79.98375479721732</v>
       </c>
       <c r="E60">
-        <v>181.532</v>
+        <v>185.586</v>
       </c>
       <c r="F60">
-        <v>235.132</v>
+        <v>239.186</v>
       </c>
       <c r="G60">
         <v>27</v>
@@ -6207,37 +6207,37 @@
         <v>19.74</v>
       </c>
       <c r="M60">
-        <v>55.44412560000001</v>
+        <v>56.4000588</v>
       </c>
       <c r="N60">
-        <v>-35.7041256</v>
+        <v>-36.6600588</v>
       </c>
       <c r="O60">
-        <v>-3.570412560000001</v>
+        <v>-3.66600588</v>
       </c>
       <c r="P60">
-        <v>-32.13371304</v>
+        <v>-32.99405292</v>
       </c>
       <c r="Q60">
-        <v>-26.57371304</v>
+        <v>-27.43405292</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.111514674807483</v>
+        <v>0.113117471754007</v>
       </c>
       <c r="T60">
-        <v>1.3171625973556</v>
+        <v>1.349288514364273</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03560341115741214</v>
+        <v>0.03499996351067634</v>
       </c>
       <c r="W60">
-        <v>0.2274047156490822</v>
+        <v>0.2275470086041825</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3560341115741213</v>
+        <v>0.3499996351067635</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1806308984956105</v>
+        <v>0.1825308984956105</v>
       </c>
       <c r="C61">
-        <v>-132.2022452027827</v>
+        <v>-137.3676921089814</v>
       </c>
       <c r="D61">
-        <v>79.98375479721732</v>
+        <v>78.87230789101861</v>
       </c>
       <c r="E61">
-        <v>185.586</v>
+        <v>189.64</v>
       </c>
       <c r="F61">
-        <v>239.186</v>
+        <v>243.24</v>
       </c>
       <c r="G61">
         <v>27</v>
@@ -6289,37 +6289,37 @@
         <v>19.74</v>
       </c>
       <c r="M61">
-        <v>56.4000588</v>
+        <v>57.35599200000001</v>
       </c>
       <c r="N61">
-        <v>-36.6600588</v>
+        <v>-37.61599200000001</v>
       </c>
       <c r="O61">
-        <v>-3.66600588</v>
+        <v>-3.761599200000001</v>
       </c>
       <c r="P61">
-        <v>-32.99405292</v>
+        <v>-33.85439280000001</v>
       </c>
       <c r="Q61">
-        <v>-27.43405292</v>
+        <v>-28.29439280000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.113117471754007</v>
+        <v>0.1148004085478571</v>
       </c>
       <c r="T61">
-        <v>1.349288514364273</v>
+        <v>1.38302072722338</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03499996351067634</v>
+        <v>0.0344166307854984</v>
       </c>
       <c r="W61">
-        <v>0.2275470086041825</v>
+        <v>0.2276845584607795</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3499996351067635</v>
+        <v>0.344166307854984</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1825308984956105</v>
+        <v>0.1844308984956106</v>
       </c>
       <c r="C62">
-        <v>-137.3676921089814</v>
+        <v>-142.5026732367037</v>
       </c>
       <c r="D62">
-        <v>78.87230789101861</v>
+        <v>77.79132676329634</v>
       </c>
       <c r="E62">
-        <v>189.64</v>
+        <v>193.694</v>
       </c>
       <c r="F62">
-        <v>243.24</v>
+        <v>247.294</v>
       </c>
       <c r="G62">
         <v>27</v>
@@ -6371,37 +6371,37 @@
         <v>19.74</v>
       </c>
       <c r="M62">
-        <v>57.35599200000001</v>
+        <v>58.3119252</v>
       </c>
       <c r="N62">
-        <v>-37.61599200000001</v>
+        <v>-38.5719252</v>
       </c>
       <c r="O62">
-        <v>-3.761599200000001</v>
+        <v>-3.85719252</v>
       </c>
       <c r="P62">
-        <v>-33.85439280000001</v>
+        <v>-34.71473268</v>
       </c>
       <c r="Q62">
-        <v>-28.29439280000001</v>
+        <v>-29.15473268000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1148004085478571</v>
+        <v>0.116569649792674</v>
       </c>
       <c r="T62">
-        <v>1.38302072722338</v>
+        <v>1.418482797152185</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0344166307854984</v>
+        <v>0.03385242372344105</v>
       </c>
       <c r="W62">
-        <v>0.2276845584607795</v>
+        <v>0.2278175984860126</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.344166307854984</v>
+        <v>0.3385242372344105</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1844308984956106</v>
+        <v>0.1863308984956106</v>
       </c>
       <c r="C63">
-        <v>-142.5026732367037</v>
+        <v>-147.6084242923968</v>
       </c>
       <c r="D63">
-        <v>77.79132676329634</v>
+        <v>76.73957570760322</v>
       </c>
       <c r="E63">
-        <v>193.694</v>
+        <v>197.748</v>
       </c>
       <c r="F63">
-        <v>247.294</v>
+        <v>251.348</v>
       </c>
       <c r="G63">
         <v>27</v>
@@ -6453,37 +6453,37 @@
         <v>19.74</v>
       </c>
       <c r="M63">
-        <v>58.3119252</v>
+        <v>59.26785840000001</v>
       </c>
       <c r="N63">
-        <v>-38.5719252</v>
+        <v>-39.52785840000001</v>
       </c>
       <c r="O63">
-        <v>-3.85719252</v>
+        <v>-3.952785840000001</v>
       </c>
       <c r="P63">
-        <v>-34.71473268</v>
+        <v>-35.57507256000001</v>
       </c>
       <c r="Q63">
-        <v>-29.15473268000001</v>
+        <v>-30.01507256000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.116569649792674</v>
+        <v>0.1184320089977444</v>
       </c>
       <c r="T63">
-        <v>1.418482797152185</v>
+        <v>1.455811291814084</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03385242372344105</v>
+        <v>0.033306416889192</v>
       </c>
       <c r="W63">
-        <v>0.2278175984860126</v>
+        <v>0.2279463468975285</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3385242372344105</v>
+        <v>0.33306416889192</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1863308984956106</v>
+        <v>0.1882308984956105</v>
       </c>
       <c r="C64">
-        <v>-147.6084242923968</v>
+        <v>-152.6861150461902</v>
       </c>
       <c r="D64">
-        <v>76.73957570760322</v>
+        <v>75.71588495380981</v>
       </c>
       <c r="E64">
-        <v>197.748</v>
+        <v>201.802</v>
       </c>
       <c r="F64">
-        <v>251.348</v>
+        <v>255.402</v>
       </c>
       <c r="G64">
         <v>27</v>
@@ -6535,37 +6535,37 @@
         <v>19.74</v>
       </c>
       <c r="M64">
-        <v>59.26785840000001</v>
+        <v>60.22379160000001</v>
       </c>
       <c r="N64">
-        <v>-39.52785840000001</v>
+        <v>-40.4837916</v>
       </c>
       <c r="O64">
-        <v>-3.952785840000001</v>
+        <v>-4.048379160000001</v>
       </c>
       <c r="P64">
-        <v>-35.57507256000001</v>
+        <v>-36.43541244</v>
       </c>
       <c r="Q64">
-        <v>-30.01507256000001</v>
+        <v>-30.87541244</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1184320089977444</v>
+        <v>0.1203950362679537</v>
       </c>
       <c r="T64">
-        <v>1.455811291814084</v>
+        <v>1.495157542944194</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.033306416889192</v>
+        <v>0.03277774360523657</v>
       </c>
       <c r="W64">
-        <v>0.2279463468975285</v>
+        <v>0.2280710080578852</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.33306416889192</v>
+        <v>0.3277774360523658</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1882308984956105</v>
+        <v>0.1901308984956106</v>
       </c>
       <c r="C65">
-        <v>-152.6861150461902</v>
+        <v>-157.736853671888</v>
       </c>
       <c r="D65">
-        <v>75.71588495380981</v>
+        <v>74.719146328112</v>
       </c>
       <c r="E65">
-        <v>201.802</v>
+        <v>205.856</v>
       </c>
       <c r="F65">
-        <v>255.402</v>
+        <v>259.456</v>
       </c>
       <c r="G65">
         <v>27</v>
@@ -6617,37 +6617,37 @@
         <v>19.74</v>
       </c>
       <c r="M65">
-        <v>60.22379160000001</v>
+        <v>61.17972480000001</v>
       </c>
       <c r="N65">
-        <v>-40.4837916</v>
+        <v>-41.43972480000001</v>
       </c>
       <c r="O65">
-        <v>-4.048379160000001</v>
+        <v>-4.143972480000001</v>
       </c>
       <c r="P65">
-        <v>-36.43541244</v>
+        <v>-37.29575232000001</v>
       </c>
       <c r="Q65">
-        <v>-30.87541244</v>
+        <v>-31.73575232000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1203950362679537</v>
+        <v>0.1224671206087302</v>
       </c>
       <c r="T65">
-        <v>1.495157542944194</v>
+        <v>1.536689696914867</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03277774360523657</v>
+        <v>0.03226559136140475</v>
       </c>
       <c r="W65">
-        <v>0.2280710080578852</v>
+        <v>0.2281917735569808</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3277774360523658</v>
+        <v>0.3226559136140474</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1901308984956106</v>
+        <v>0.1920308984956106</v>
       </c>
       <c r="C66">
-        <v>-157.736853671888</v>
+        <v>-162.7616907486203</v>
       </c>
       <c r="D66">
-        <v>74.719146328112</v>
+        <v>73.74830925137975</v>
       </c>
       <c r="E66">
-        <v>205.856</v>
+        <v>209.91</v>
       </c>
       <c r="F66">
-        <v>259.456</v>
+        <v>263.51</v>
       </c>
       <c r="G66">
         <v>27</v>
@@ -6699,37 +6699,37 @@
         <v>19.74</v>
       </c>
       <c r="M66">
-        <v>61.17972480000001</v>
+        <v>62.13565800000001</v>
       </c>
       <c r="N66">
-        <v>-41.43972480000001</v>
+        <v>-42.39565800000001</v>
       </c>
       <c r="O66">
-        <v>-4.143972480000001</v>
+        <v>-4.239565800000001</v>
       </c>
       <c r="P66">
-        <v>-37.29575232000001</v>
+        <v>-38.15609220000001</v>
       </c>
       <c r="Q66">
-        <v>-31.73575232000001</v>
+        <v>-32.59609220000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1224671206087302</v>
+        <v>0.1246576097689796</v>
       </c>
       <c r="T66">
-        <v>1.536689696914867</v>
+        <v>1.58059511682672</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03226559136140475</v>
+        <v>0.03176919764815236</v>
       </c>
       <c r="W66">
-        <v>0.2281917735569808</v>
+        <v>0.2283088231945657</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3226559136140474</v>
+        <v>0.3176919764815237</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1920308984956106</v>
+        <v>0.1939308984956106</v>
       </c>
       <c r="C67">
-        <v>-162.7616907486203</v>
+        <v>-167.7616229545319</v>
       </c>
       <c r="D67">
-        <v>73.74830925137975</v>
+        <v>72.80237704546813</v>
       </c>
       <c r="E67">
-        <v>209.91</v>
+        <v>213.964</v>
       </c>
       <c r="F67">
-        <v>263.51</v>
+        <v>267.564</v>
       </c>
       <c r="G67">
         <v>27</v>
@@ -6781,37 +6781,37 @@
         <v>19.74</v>
       </c>
       <c r="M67">
-        <v>62.13565800000001</v>
+        <v>63.09159120000001</v>
       </c>
       <c r="N67">
-        <v>-42.39565800000001</v>
+        <v>-43.35159120000001</v>
       </c>
       <c r="O67">
-        <v>-4.239565800000001</v>
+        <v>-4.335159120000001</v>
       </c>
       <c r="P67">
-        <v>-38.15609220000001</v>
+        <v>-39.01643208000001</v>
       </c>
       <c r="Q67">
-        <v>-32.59609220000001</v>
+        <v>-33.45643208000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1246576097689796</v>
+        <v>0.1269769512327731</v>
       </c>
       <c r="T67">
-        <v>1.58059511682672</v>
+        <v>1.627083208498094</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03176919764815236</v>
+        <v>0.03128784616863491</v>
       </c>
       <c r="W67">
-        <v>0.2283088231945657</v>
+        <v>0.2284223258734359</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3176919764815237</v>
+        <v>0.312878461686349</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1939308984956106</v>
+        <v>0.1958308984956106</v>
       </c>
       <c r="C68">
-        <v>-167.7616229545319</v>
+        <v>-172.7375964798083</v>
       </c>
       <c r="D68">
-        <v>72.80237704546813</v>
+        <v>71.88040352019172</v>
       </c>
       <c r="E68">
-        <v>213.964</v>
+        <v>218.018</v>
       </c>
       <c r="F68">
-        <v>267.564</v>
+        <v>271.6180000000001</v>
       </c>
       <c r="G68">
         <v>27</v>
@@ -6863,37 +6863,37 @@
         <v>19.74</v>
       </c>
       <c r="M68">
-        <v>63.09159120000001</v>
+        <v>64.04752440000001</v>
       </c>
       <c r="N68">
-        <v>-43.35159120000001</v>
+        <v>-44.30752440000001</v>
       </c>
       <c r="O68">
-        <v>-4.335159120000001</v>
+        <v>-4.430752440000002</v>
       </c>
       <c r="P68">
-        <v>-39.01643208000001</v>
+        <v>-39.87677196000001</v>
       </c>
       <c r="Q68">
-        <v>-33.45643208000001</v>
+        <v>-34.31677196000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1269769512327731</v>
+        <v>0.1294368588458875</v>
       </c>
       <c r="T68">
-        <v>1.627083208498094</v>
+        <v>1.676388760270764</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03128784616863491</v>
+        <v>0.03082086338999857</v>
       </c>
       <c r="W68">
-        <v>0.2284223258734359</v>
+        <v>0.2285324404126383</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.312878461686349</v>
+        <v>0.3082086338999857</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1958308984956106</v>
+        <v>0.1977308984956106</v>
       </c>
       <c r="C69">
-        <v>-172.7375964798083</v>
+        <v>-177.6905101836084</v>
       </c>
       <c r="D69">
-        <v>71.88040352019172</v>
+        <v>70.98148981639159</v>
       </c>
       <c r="E69">
-        <v>218.018</v>
+        <v>222.072</v>
       </c>
       <c r="F69">
-        <v>271.6180000000001</v>
+        <v>275.672</v>
       </c>
       <c r="G69">
         <v>27</v>
@@ -6945,37 +6945,37 @@
         <v>19.74</v>
       </c>
       <c r="M69">
-        <v>64.04752440000001</v>
+        <v>65.0034576</v>
       </c>
       <c r="N69">
-        <v>-44.30752440000001</v>
+        <v>-45.2634576</v>
       </c>
       <c r="O69">
-        <v>-4.430752440000002</v>
+        <v>-4.526345760000001</v>
       </c>
       <c r="P69">
-        <v>-39.87677196000001</v>
+        <v>-40.73711184</v>
       </c>
       <c r="Q69">
-        <v>-34.31677196000001</v>
+        <v>-35.17711184</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1294368588458875</v>
+        <v>0.1320505106848215</v>
       </c>
       <c r="T69">
-        <v>1.676388760270764</v>
+        <v>1.728775909029225</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03082086338999857</v>
+        <v>0.03036761539896918</v>
       </c>
       <c r="W69">
-        <v>0.2285324404126383</v>
+        <v>0.2286393162889231</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3082086338999857</v>
+        <v>0.3036761539896918</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1977308984956106</v>
+        <v>0.1996308984956106</v>
       </c>
       <c r="C70">
-        <v>-177.6905101836084</v>
+        <v>-182.6212185170451</v>
       </c>
       <c r="D70">
-        <v>70.98148981639159</v>
+        <v>70.10478148295495</v>
       </c>
       <c r="E70">
-        <v>222.072</v>
+        <v>226.126</v>
       </c>
       <c r="F70">
-        <v>275.672</v>
+        <v>279.7260000000001</v>
       </c>
       <c r="G70">
         <v>27</v>
@@ -7027,37 +7027,37 @@
         <v>19.74</v>
       </c>
       <c r="M70">
-        <v>65.0034576</v>
+        <v>65.95939080000002</v>
       </c>
       <c r="N70">
-        <v>-45.2634576</v>
+        <v>-46.21939080000002</v>
       </c>
       <c r="O70">
-        <v>-4.526345760000001</v>
+        <v>-4.621939080000002</v>
       </c>
       <c r="P70">
-        <v>-40.73711184</v>
+        <v>-41.59745172000002</v>
       </c>
       <c r="Q70">
-        <v>-35.17711184</v>
+        <v>-36.03745172000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1320505106848215</v>
+        <v>0.1348327852230415</v>
       </c>
       <c r="T70">
-        <v>1.728775909029225</v>
+        <v>1.78454287383662</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03036761539896918</v>
+        <v>0.02992750503086817</v>
       </c>
       <c r="W70">
-        <v>0.2286393162889231</v>
+        <v>0.2287430943137213</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3036761539896918</v>
+        <v>0.2992750503086816</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1996308984956106</v>
+        <v>0.2015308984956106</v>
       </c>
       <c r="C71">
-        <v>-182.6212185170451</v>
+        <v>-187.5305342321943</v>
       </c>
       <c r="D71">
-        <v>70.10478148295495</v>
+        <v>69.24946576780576</v>
       </c>
       <c r="E71">
-        <v>226.126</v>
+        <v>230.18</v>
       </c>
       <c r="F71">
-        <v>279.7260000000001</v>
+        <v>283.78</v>
       </c>
       <c r="G71">
         <v>27</v>
@@ -7109,37 +7109,37 @@
         <v>19.74</v>
       </c>
       <c r="M71">
-        <v>65.95939080000002</v>
+        <v>66.91532400000001</v>
       </c>
       <c r="N71">
-        <v>-46.21939080000002</v>
+        <v>-47.17532400000001</v>
       </c>
       <c r="O71">
-        <v>-4.621939080000002</v>
+        <v>-4.717532400000001</v>
       </c>
       <c r="P71">
-        <v>-41.59745172000002</v>
+        <v>-42.45779160000001</v>
       </c>
       <c r="Q71">
-        <v>-36.03745172000001</v>
+        <v>-36.89779160000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1348327852230415</v>
+        <v>0.1378005447304762</v>
       </c>
       <c r="T71">
-        <v>1.78454287383662</v>
+        <v>1.84402763629784</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02992750503086817</v>
+        <v>0.02949996924471292</v>
       </c>
       <c r="W71">
-        <v>0.2287430943137213</v>
+        <v>0.2288439072520967</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2992750503086816</v>
+        <v>0.2949996924471291</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2015308984956106</v>
+        <v>0.2034308984956106</v>
       </c>
       <c r="C72">
-        <v>-187.5305342321943</v>
+        <v>-192.4192308951871</v>
       </c>
       <c r="D72">
-        <v>69.24946576780576</v>
+        <v>68.414769104813</v>
       </c>
       <c r="E72">
-        <v>230.18</v>
+        <v>234.234</v>
       </c>
       <c r="F72">
-        <v>283.78</v>
+        <v>287.8340000000001</v>
       </c>
       <c r="G72">
         <v>27</v>
@@ -7191,37 +7191,37 @@
         <v>19.74</v>
       </c>
       <c r="M72">
-        <v>66.91532400000001</v>
+        <v>67.87125720000002</v>
       </c>
       <c r="N72">
-        <v>-47.17532400000001</v>
+        <v>-48.13125720000001</v>
       </c>
       <c r="O72">
-        <v>-4.717532400000001</v>
+        <v>-4.813125720000002</v>
       </c>
       <c r="P72">
-        <v>-42.45779160000001</v>
+        <v>-43.31813148000001</v>
       </c>
       <c r="Q72">
-        <v>-36.89779160000001</v>
+        <v>-37.75813148000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1378005447304762</v>
+        <v>0.1409729773073892</v>
       </c>
       <c r="T72">
-        <v>1.84402763629784</v>
+        <v>1.90761479617018</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02949996924471292</v>
+        <v>0.02908447672013949</v>
       </c>
       <c r="W72">
-        <v>0.2288439072520967</v>
+        <v>0.2289418803893911</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2949996924471291</v>
+        <v>0.2908447672013948</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2034308984956106</v>
+        <v>0.2053308984956106</v>
       </c>
       <c r="C73">
-        <v>-192.419230895187</v>
+        <v>-197.2880452197157</v>
       </c>
       <c r="D73">
-        <v>68.41476910481296</v>
+        <v>67.59995478028435</v>
       </c>
       <c r="E73">
-        <v>234.234</v>
+        <v>238.288</v>
       </c>
       <c r="F73">
-        <v>287.834</v>
+        <v>291.888</v>
       </c>
       <c r="G73">
         <v>27</v>
@@ -7273,37 +7273,37 @@
         <v>19.74</v>
       </c>
       <c r="M73">
-        <v>67.8712572</v>
+        <v>68.82719040000001</v>
       </c>
       <c r="N73">
-        <v>-48.1312572</v>
+        <v>-49.0871904</v>
       </c>
       <c r="O73">
-        <v>-4.81312572</v>
+        <v>-4.908719040000001</v>
       </c>
       <c r="P73">
-        <v>-43.31813148</v>
+        <v>-44.17847136</v>
       </c>
       <c r="Q73">
-        <v>-37.75813148</v>
+        <v>-38.61847136</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1409729773073892</v>
+        <v>0.1443720122112245</v>
       </c>
       <c r="T73">
-        <v>1.907614796170179</v>
+        <v>1.9757438960334</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0290844767201395</v>
+        <v>0.028680525654582</v>
       </c>
       <c r="W73">
-        <v>0.2289418803893911</v>
+        <v>0.2290371320506496</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.290844767201395</v>
+        <v>0.28680525654582</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2053308984956106</v>
+        <v>0.2072308984956105</v>
       </c>
       <c r="C74">
-        <v>-197.2880452197157</v>
+        <v>-202.1376792357527</v>
       </c>
       <c r="D74">
-        <v>67.59995478028435</v>
+        <v>66.80432076424731</v>
       </c>
       <c r="E74">
-        <v>238.288</v>
+        <v>242.342</v>
       </c>
       <c r="F74">
-        <v>291.888</v>
+        <v>295.942</v>
       </c>
       <c r="G74">
         <v>27</v>
@@ -7355,37 +7355,37 @@
         <v>19.74</v>
       </c>
       <c r="M74">
-        <v>68.82719040000001</v>
+        <v>69.78312360000001</v>
       </c>
       <c r="N74">
-        <v>-49.0871904</v>
+        <v>-50.04312360000001</v>
       </c>
       <c r="O74">
-        <v>-4.908719040000001</v>
+        <v>-5.004312360000001</v>
       </c>
       <c r="P74">
-        <v>-44.17847136</v>
+        <v>-45.03881124000001</v>
       </c>
       <c r="Q74">
-        <v>-38.61847136</v>
+        <v>-39.47881124000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1443720122112245</v>
+        <v>0.1480228274783069</v>
       </c>
       <c r="T74">
-        <v>1.9757438960334</v>
+        <v>2.048919595886488</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.028680525654582</v>
+        <v>0.02828764174150553</v>
       </c>
       <c r="W74">
-        <v>0.2290371320506496</v>
+        <v>0.229129774077353</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.28680525654582</v>
+        <v>0.2828764174150553</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2072308984956105</v>
+        <v>0.2091308984956106</v>
       </c>
       <c r="C75">
-        <v>-202.1376792357527</v>
+        <v>-206.9688023068995</v>
       </c>
       <c r="D75">
-        <v>66.80432076424731</v>
+        <v>66.02719769310053</v>
       </c>
       <c r="E75">
-        <v>242.342</v>
+        <v>246.396</v>
       </c>
       <c r="F75">
-        <v>295.942</v>
+        <v>299.996</v>
       </c>
       <c r="G75">
         <v>27</v>
@@ -7437,37 +7437,37 @@
         <v>19.74</v>
       </c>
       <c r="M75">
-        <v>69.78312360000001</v>
+        <v>70.73905680000001</v>
       </c>
       <c r="N75">
-        <v>-50.04312360000001</v>
+        <v>-50.99905680000001</v>
       </c>
       <c r="O75">
-        <v>-5.004312360000001</v>
+        <v>-5.099905680000002</v>
       </c>
       <c r="P75">
-        <v>-45.03881124000001</v>
+        <v>-45.89915112000001</v>
       </c>
       <c r="Q75">
-        <v>-39.47881124000001</v>
+        <v>-40.33915112000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1480228274783069</v>
+        <v>0.151954474689011</v>
       </c>
       <c r="T75">
-        <v>2.048919595886488</v>
+        <v>2.127724195728276</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02828764174150553</v>
+        <v>0.02790537631256627</v>
       </c>
       <c r="W75">
-        <v>0.229129774077353</v>
+        <v>0.2292199122654969</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2828764174150553</v>
+        <v>0.2790537631256627</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2091308984956106</v>
+        <v>0.2110308984956105</v>
       </c>
       <c r="C76">
-        <v>-206.9688023068995</v>
+        <v>-211.7820530085485</v>
       </c>
       <c r="D76">
-        <v>66.02719769310053</v>
+        <v>65.26794699145147</v>
       </c>
       <c r="E76">
-        <v>246.396</v>
+        <v>250.45</v>
       </c>
       <c r="F76">
-        <v>299.996</v>
+        <v>304.05</v>
       </c>
       <c r="G76">
         <v>27</v>
@@ -7519,37 +7519,37 @@
         <v>19.74</v>
       </c>
       <c r="M76">
-        <v>70.73905680000001</v>
+        <v>71.69499</v>
       </c>
       <c r="N76">
-        <v>-50.99905680000001</v>
+        <v>-51.95499</v>
       </c>
       <c r="O76">
-        <v>-5.099905680000002</v>
+        <v>-5.195499000000001</v>
       </c>
       <c r="P76">
-        <v>-45.89915112000001</v>
+        <v>-46.759491</v>
       </c>
       <c r="Q76">
-        <v>-40.33915112000001</v>
+        <v>-41.199491</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.151954474689011</v>
+        <v>0.1562006536765715</v>
       </c>
       <c r="T76">
-        <v>2.127724195728276</v>
+        <v>2.212833163557408</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02790537631256627</v>
+        <v>0.02753330462839872</v>
       </c>
       <c r="W76">
-        <v>0.2292199122654969</v>
+        <v>0.2293076467686236</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2790537631256627</v>
+        <v>0.2753330462839872</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2110308984956105</v>
+        <v>0.2129308984956106</v>
       </c>
       <c r="C77">
-        <v>-211.7820530085485</v>
+        <v>-216.5780408779371</v>
       </c>
       <c r="D77">
-        <v>65.26794699145147</v>
+        <v>64.52595912206293</v>
       </c>
       <c r="E77">
-        <v>250.45</v>
+        <v>254.504</v>
       </c>
       <c r="F77">
-        <v>304.05</v>
+        <v>308.104</v>
       </c>
       <c r="G77">
         <v>27</v>
@@ -7601,37 +7601,37 @@
         <v>19.74</v>
       </c>
       <c r="M77">
-        <v>71.69499</v>
+        <v>72.65092320000001</v>
       </c>
       <c r="N77">
-        <v>-51.95499</v>
+        <v>-52.91092320000001</v>
       </c>
       <c r="O77">
-        <v>-5.195499000000001</v>
+        <v>-5.291092320000001</v>
       </c>
       <c r="P77">
-        <v>-46.759491</v>
+        <v>-47.61983088000001</v>
       </c>
       <c r="Q77">
-        <v>-41.199491</v>
+        <v>-42.05983088000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1562006536765715</v>
+        <v>0.1608006809130953</v>
       </c>
       <c r="T77">
-        <v>2.212833163557408</v>
+        <v>2.3050345453723</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02753330462839872</v>
+        <v>0.02717102430434084</v>
       </c>
       <c r="W77">
-        <v>0.2293076467686236</v>
+        <v>0.2293930724690365</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2753330462839872</v>
+        <v>0.2717102430434084</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2129308984956106</v>
+        <v>0.2148308984956105</v>
       </c>
       <c r="C78">
-        <v>-216.5780408779371</v>
+        <v>-221.3573480461712</v>
       </c>
       <c r="D78">
-        <v>64.52595912206293</v>
+        <v>63.80065195382883</v>
       </c>
       <c r="E78">
-        <v>254.504</v>
+        <v>258.558</v>
       </c>
       <c r="F78">
-        <v>308.104</v>
+        <v>312.158</v>
       </c>
       <c r="G78">
         <v>27</v>
@@ -7683,37 +7683,37 @@
         <v>19.74</v>
       </c>
       <c r="M78">
-        <v>72.65092320000001</v>
+        <v>73.60685640000001</v>
       </c>
       <c r="N78">
-        <v>-52.91092320000001</v>
+        <v>-53.86685640000001</v>
       </c>
       <c r="O78">
-        <v>-5.291092320000001</v>
+        <v>-5.386685640000001</v>
       </c>
       <c r="P78">
-        <v>-47.61983088000001</v>
+        <v>-48.48017076000001</v>
       </c>
       <c r="Q78">
-        <v>-42.05983088000001</v>
+        <v>-42.92017076</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1608006809130953</v>
+        <v>0.1658007105180124</v>
       </c>
       <c r="T78">
-        <v>2.3050345453723</v>
+        <v>2.405253438649356</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02717102430434084</v>
+        <v>0.02681815385882992</v>
       </c>
       <c r="W78">
-        <v>0.2293930724690365</v>
+        <v>0.2294762793200879</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2717102430434084</v>
+        <v>0.2681815385882992</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2148308984956105</v>
+        <v>0.2167308984956106</v>
       </c>
       <c r="C79">
-        <v>-221.3573480461712</v>
+        <v>-226.1205307614039</v>
       </c>
       <c r="D79">
-        <v>63.80065195382883</v>
+        <v>63.09146923859617</v>
       </c>
       <c r="E79">
-        <v>258.558</v>
+        <v>262.612</v>
       </c>
       <c r="F79">
-        <v>312.158</v>
+        <v>316.212</v>
       </c>
       <c r="G79">
         <v>27</v>
@@ -7765,37 +7765,37 @@
         <v>19.74</v>
       </c>
       <c r="M79">
-        <v>73.60685640000001</v>
+        <v>74.56278960000002</v>
       </c>
       <c r="N79">
-        <v>-53.86685640000001</v>
+        <v>-54.82278960000001</v>
       </c>
       <c r="O79">
-        <v>-5.386685640000001</v>
+        <v>-5.482278960000002</v>
       </c>
       <c r="P79">
-        <v>-48.48017076000001</v>
+        <v>-49.34051064000001</v>
       </c>
       <c r="Q79">
-        <v>-42.92017076</v>
+        <v>-43.78051064000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1658007105180124</v>
+        <v>0.1712552882688312</v>
       </c>
       <c r="T79">
-        <v>2.405253438649356</v>
+        <v>2.514583140406145</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02681815385882992</v>
+        <v>0.0264743313734603</v>
       </c>
       <c r="W79">
-        <v>0.2294762793200879</v>
+        <v>0.2295573526621381</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2681815385882992</v>
+        <v>0.264743313734603</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2167308984956106</v>
+        <v>0.2186308984956106</v>
       </c>
       <c r="C80">
-        <v>-226.1205307614039</v>
+        <v>-230.868120811544</v>
       </c>
       <c r="D80">
-        <v>63.09146923859617</v>
+        <v>62.39787918845603</v>
       </c>
       <c r="E80">
-        <v>262.612</v>
+        <v>266.666</v>
       </c>
       <c r="F80">
-        <v>316.212</v>
+        <v>320.266</v>
       </c>
       <c r="G80">
         <v>27</v>
@@ -7847,37 +7847,37 @@
         <v>19.74</v>
       </c>
       <c r="M80">
-        <v>74.56278960000002</v>
+        <v>75.51872280000001</v>
       </c>
       <c r="N80">
-        <v>-54.82278960000001</v>
+        <v>-55.7787228</v>
       </c>
       <c r="O80">
-        <v>-5.482278960000002</v>
+        <v>-5.577872280000001</v>
       </c>
       <c r="P80">
-        <v>-49.34051064000001</v>
+        <v>-50.20085052</v>
       </c>
       <c r="Q80">
-        <v>-43.78051064000001</v>
+        <v>-44.64085052</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1712552882688312</v>
+        <v>0.177229349614966</v>
       </c>
       <c r="T80">
-        <v>2.514583140406145</v>
+        <v>2.6343251947112</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0264743313734603</v>
+        <v>0.02613921325480891</v>
       </c>
       <c r="W80">
-        <v>0.2295573526621381</v>
+        <v>0.2296363735145161</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.264743313734603</v>
+        <v>0.2613921325480891</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2186308984956106</v>
+        <v>0.2205308984956106</v>
       </c>
       <c r="C81">
-        <v>-230.868120811544</v>
+        <v>-235.6006268541433</v>
       </c>
       <c r="D81">
-        <v>62.39787918845603</v>
+        <v>61.71937314585674</v>
       </c>
       <c r="E81">
-        <v>266.666</v>
+        <v>270.72</v>
       </c>
       <c r="F81">
-        <v>320.266</v>
+        <v>324.3200000000001</v>
       </c>
       <c r="G81">
         <v>27</v>
@@ -7929,37 +7929,37 @@
         <v>19.74</v>
       </c>
       <c r="M81">
-        <v>75.51872280000001</v>
+        <v>76.47465600000001</v>
       </c>
       <c r="N81">
-        <v>-55.7787228</v>
+        <v>-56.73465600000001</v>
       </c>
       <c r="O81">
-        <v>-5.577872280000001</v>
+        <v>-5.673465600000001</v>
       </c>
       <c r="P81">
-        <v>-50.20085052</v>
+        <v>-51.06119040000001</v>
       </c>
       <c r="Q81">
-        <v>-44.64085052</v>
+        <v>-45.50119040000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.177229349614966</v>
+        <v>0.1838008170957144</v>
       </c>
       <c r="T81">
-        <v>2.6343251947112</v>
+        <v>2.76604145444676</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02613921325480891</v>
+        <v>0.0258124730891238</v>
       </c>
       <c r="W81">
-        <v>0.2296363735145161</v>
+        <v>0.2297134188455846</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2613921325480891</v>
+        <v>0.258124730891238</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2205308984956106</v>
+        <v>0.2224308984956105</v>
       </c>
       <c r="C82">
-        <v>-235.6006268541433</v>
+        <v>-240.3185356604501</v>
       </c>
       <c r="D82">
-        <v>61.71937314585674</v>
+        <v>61.05546433954995</v>
       </c>
       <c r="E82">
-        <v>270.72</v>
+        <v>274.774</v>
       </c>
       <c r="F82">
-        <v>324.3200000000001</v>
+        <v>328.374</v>
       </c>
       <c r="G82">
         <v>27</v>
@@ -8011,37 +8011,37 @@
         <v>19.74</v>
       </c>
       <c r="M82">
-        <v>76.47465600000001</v>
+        <v>77.43058920000001</v>
       </c>
       <c r="N82">
-        <v>-56.73465600000001</v>
+        <v>-57.69058920000001</v>
       </c>
       <c r="O82">
-        <v>-5.673465600000001</v>
+        <v>-5.769058920000002</v>
       </c>
       <c r="P82">
-        <v>-51.06119040000001</v>
+        <v>-51.92153028000001</v>
       </c>
       <c r="Q82">
-        <v>-45.50119040000001</v>
+        <v>-46.36153028000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1838008170957144</v>
+        <v>0.1910640179954888</v>
       </c>
       <c r="T82">
-        <v>2.76604145444676</v>
+        <v>2.911622583628169</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0258124730891238</v>
+        <v>0.02549380058185067</v>
       </c>
       <c r="W82">
-        <v>0.2297134188455846</v>
+        <v>0.2297885618227996</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.258124730891238</v>
+        <v>0.2549380058185067</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2224308984956105</v>
+        <v>0.2243308984956106</v>
       </c>
       <c r="C83">
-        <v>-240.3185356604501</v>
+        <v>-245.0223132800256</v>
       </c>
       <c r="D83">
-        <v>61.05546433954995</v>
+        <v>60.40568671997443</v>
       </c>
       <c r="E83">
-        <v>274.774</v>
+        <v>278.828</v>
       </c>
       <c r="F83">
-        <v>328.374</v>
+        <v>332.4280000000001</v>
       </c>
       <c r="G83">
         <v>27</v>
@@ -8093,37 +8093,37 @@
         <v>19.74</v>
       </c>
       <c r="M83">
-        <v>77.43058920000001</v>
+        <v>78.38652240000002</v>
       </c>
       <c r="N83">
-        <v>-57.69058920000001</v>
+        <v>-58.64652240000002</v>
       </c>
       <c r="O83">
-        <v>-5.769058920000002</v>
+        <v>-5.864652240000002</v>
       </c>
       <c r="P83">
-        <v>-51.92153028000001</v>
+        <v>-52.78187016000001</v>
       </c>
       <c r="Q83">
-        <v>-46.36153028000001</v>
+        <v>-47.22187016000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1910640179954888</v>
+        <v>0.1991342412174604</v>
       </c>
       <c r="T83">
-        <v>2.911622583628169</v>
+        <v>3.073379393829734</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02549380058185067</v>
+        <v>0.02518290057475493</v>
       </c>
       <c r="W83">
-        <v>0.2297885618227996</v>
+        <v>0.2298618720444728</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2549380058185067</v>
+        <v>0.2518290057475493</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2243308984956106</v>
+        <v>0.2262308984956106</v>
       </c>
       <c r="C84">
-        <v>-245.0223132800256</v>
+        <v>-249.7124061317759</v>
       </c>
       <c r="D84">
-        <v>60.40568671997443</v>
+        <v>59.76959386822414</v>
       </c>
       <c r="E84">
-        <v>278.828</v>
+        <v>282.8820000000001</v>
       </c>
       <c r="F84">
-        <v>332.4280000000001</v>
+        <v>336.4820000000001</v>
       </c>
       <c r="G84">
         <v>27</v>
@@ -8175,37 +8175,37 @@
         <v>19.74</v>
       </c>
       <c r="M84">
-        <v>78.38652240000002</v>
+        <v>79.34245560000002</v>
       </c>
       <c r="N84">
-        <v>-58.64652240000002</v>
+        <v>-59.60245560000002</v>
       </c>
       <c r="O84">
-        <v>-5.864652240000002</v>
+        <v>-5.960245560000002</v>
       </c>
       <c r="P84">
-        <v>-52.78187016000001</v>
+        <v>-53.64221004000002</v>
       </c>
       <c r="Q84">
-        <v>-47.22187016000001</v>
+        <v>-48.08221004000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1991342412174604</v>
+        <v>0.2081539024655463</v>
       </c>
       <c r="T84">
-        <v>3.073379393829734</v>
+        <v>3.254166416996189</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02518290057475493</v>
+        <v>0.02487949213409522</v>
       </c>
       <c r="W84">
-        <v>0.2298618720444728</v>
+        <v>0.2299334157547804</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2518290057475493</v>
+        <v>0.2487949213409523</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2262308984956106</v>
+        <v>0.2281308984956106</v>
       </c>
       <c r="C85">
-        <v>-249.7124061317759</v>
+        <v>-254.3892420267702</v>
       </c>
       <c r="D85">
-        <v>59.76959386822414</v>
+        <v>59.14675797322983</v>
       </c>
       <c r="E85">
-        <v>282.8820000000001</v>
+        <v>286.936</v>
       </c>
       <c r="F85">
-        <v>336.4820000000001</v>
+        <v>340.5360000000001</v>
       </c>
       <c r="G85">
         <v>27</v>
@@ -8257,37 +8257,37 @@
         <v>19.74</v>
       </c>
       <c r="M85">
-        <v>79.34245560000002</v>
+        <v>80.29838880000001</v>
       </c>
       <c r="N85">
-        <v>-59.60245560000002</v>
+        <v>-60.55838880000001</v>
       </c>
       <c r="O85">
-        <v>-5.960245560000002</v>
+        <v>-6.055838880000001</v>
       </c>
       <c r="P85">
-        <v>-53.64221004000002</v>
+        <v>-54.50254992000001</v>
       </c>
       <c r="Q85">
-        <v>-48.08221004000001</v>
+        <v>-48.94254992</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2081539024655463</v>
+        <v>0.218301021369643</v>
       </c>
       <c r="T85">
-        <v>3.254166416996189</v>
+        <v>3.457551818058452</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02487949213409522</v>
+        <v>0.02458330770392743</v>
       </c>
       <c r="W85">
-        <v>0.2299334157547804</v>
+        <v>0.2300032560434139</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2487949213409523</v>
+        <v>0.2458330770392743</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2281308984956106</v>
+        <v>0.2300308984956105</v>
       </c>
       <c r="C86">
-        <v>-254.3892420267702</v>
+        <v>-259.0532311277668</v>
       </c>
       <c r="D86">
-        <v>59.14675797322979</v>
+        <v>58.53676887223322</v>
       </c>
       <c r="E86">
-        <v>286.936</v>
+        <v>290.99</v>
       </c>
       <c r="F86">
-        <v>340.536</v>
+        <v>344.59</v>
       </c>
       <c r="G86">
         <v>27</v>
@@ -8339,37 +8339,37 @@
         <v>19.74</v>
       </c>
       <c r="M86">
-        <v>80.2983888</v>
+        <v>81.25432200000002</v>
       </c>
       <c r="N86">
-        <v>-60.5583888</v>
+        <v>-61.51432200000001</v>
       </c>
       <c r="O86">
-        <v>-6.05583888</v>
+        <v>-6.151432200000002</v>
       </c>
       <c r="P86">
-        <v>-54.50254991999999</v>
+        <v>-55.36288980000001</v>
       </c>
       <c r="Q86">
-        <v>-48.94254991999999</v>
+        <v>-49.80288980000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2183010213696429</v>
+        <v>0.2298010894609524</v>
       </c>
       <c r="T86">
-        <v>3.457551818058449</v>
+        <v>3.688055272595679</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02458330770392743</v>
+        <v>0.02429409231917534</v>
       </c>
       <c r="W86">
-        <v>0.2300032560434139</v>
+        <v>0.2300714530311385</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2458330770392744</v>
+        <v>0.2429409231917534</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2300308984956105</v>
+        <v>0.2319308984956106</v>
       </c>
       <c r="C87">
-        <v>-259.0532311277668</v>
+        <v>-263.7047668499719</v>
       </c>
       <c r="D87">
-        <v>58.53676887223322</v>
+        <v>57.93923315002815</v>
       </c>
       <c r="E87">
-        <v>290.99</v>
+        <v>295.044</v>
       </c>
       <c r="F87">
-        <v>344.59</v>
+        <v>348.644</v>
       </c>
       <c r="G87">
         <v>27</v>
@@ -8421,37 +8421,37 @@
         <v>19.74</v>
       </c>
       <c r="M87">
-        <v>81.25432200000002</v>
+        <v>82.21025520000001</v>
       </c>
       <c r="N87">
-        <v>-61.51432200000001</v>
+        <v>-62.4702552</v>
       </c>
       <c r="O87">
-        <v>-6.151432200000002</v>
+        <v>-6.247025520000001</v>
       </c>
       <c r="P87">
-        <v>-55.36288980000001</v>
+        <v>-56.22322968</v>
       </c>
       <c r="Q87">
-        <v>-49.80288980000001</v>
+        <v>-50.66322968</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2298010894609524</v>
+        <v>0.2429440244224491</v>
       </c>
       <c r="T87">
-        <v>3.688055272595679</v>
+        <v>3.9514877920668</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02429409231917534</v>
+        <v>0.02401160287360354</v>
       </c>
       <c r="W87">
-        <v>0.2300714530311385</v>
+        <v>0.2301380640424043</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2429409231917534</v>
+        <v>0.2401160287360353</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2319308984956106</v>
+        <v>0.2338308984956106</v>
       </c>
       <c r="C88">
-        <v>-263.7047668499719</v>
+        <v>-268.3442267071858</v>
       </c>
       <c r="D88">
-        <v>57.93923315002815</v>
+        <v>57.35377329281423</v>
       </c>
       <c r="E88">
-        <v>295.044</v>
+        <v>299.098</v>
       </c>
       <c r="F88">
-        <v>348.644</v>
+        <v>352.698</v>
       </c>
       <c r="G88">
         <v>27</v>
@@ -8503,37 +8503,37 @@
         <v>19.74</v>
       </c>
       <c r="M88">
-        <v>82.21025520000001</v>
+        <v>83.16618840000001</v>
       </c>
       <c r="N88">
-        <v>-62.4702552</v>
+        <v>-63.42618840000001</v>
       </c>
       <c r="O88">
-        <v>-6.247025520000001</v>
+        <v>-6.342618840000001</v>
       </c>
       <c r="P88">
-        <v>-56.22322968</v>
+        <v>-57.08356956000001</v>
       </c>
       <c r="Q88">
-        <v>-50.66322968</v>
+        <v>-51.52356956000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2429440244224491</v>
+        <v>0.258108949378022</v>
       </c>
       <c r="T88">
-        <v>3.9514877920668</v>
+        <v>4.255448391456553</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02401160287360354</v>
+        <v>0.02373560743827476</v>
       </c>
       <c r="W88">
-        <v>0.2301380640424043</v>
+        <v>0.2302031437660548</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2401160287360353</v>
+        <v>0.2373560743827476</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2338308984956106</v>
+        <v>0.2357308984956106</v>
       </c>
       <c r="C89">
-        <v>-268.3442267071858</v>
+        <v>-272.9719731071633</v>
       </c>
       <c r="D89">
-        <v>57.35377329281423</v>
+        <v>56.78002689283676</v>
       </c>
       <c r="E89">
-        <v>299.098</v>
+        <v>303.152</v>
       </c>
       <c r="F89">
-        <v>352.698</v>
+        <v>356.752</v>
       </c>
       <c r="G89">
         <v>27</v>
@@ -8585,37 +8585,37 @@
         <v>19.74</v>
       </c>
       <c r="M89">
-        <v>83.16618840000001</v>
+        <v>84.1221216</v>
       </c>
       <c r="N89">
-        <v>-63.42618840000001</v>
+        <v>-64.3821216</v>
       </c>
       <c r="O89">
-        <v>-6.342618840000001</v>
+        <v>-6.438212160000001</v>
       </c>
       <c r="P89">
-        <v>-57.08356956000001</v>
+        <v>-57.94390944000001</v>
       </c>
       <c r="Q89">
-        <v>-51.52356956000001</v>
+        <v>-52.38390944</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.258108949378022</v>
+        <v>0.2758013618261906</v>
       </c>
       <c r="T89">
-        <v>4.255448391456553</v>
+        <v>4.6100690907446</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02373560743827476</v>
+        <v>0.02346588462647619</v>
       </c>
       <c r="W89">
-        <v>0.2302031437660548</v>
+        <v>0.2302667444050769</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2373560743827476</v>
+        <v>0.2346588462647617</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2357308984956106</v>
+        <v>0.2376308984956106</v>
       </c>
       <c r="C90">
-        <v>-272.9719731071633</v>
+        <v>-277.5883540997064</v>
       </c>
       <c r="D90">
-        <v>56.78002689283676</v>
+        <v>56.21764590029363</v>
       </c>
       <c r="E90">
-        <v>303.152</v>
+        <v>307.206</v>
       </c>
       <c r="F90">
-        <v>356.752</v>
+        <v>360.806</v>
       </c>
       <c r="G90">
         <v>27</v>
@@ -8667,37 +8667,37 @@
         <v>19.74</v>
       </c>
       <c r="M90">
-        <v>84.1221216</v>
+        <v>85.07805480000002</v>
       </c>
       <c r="N90">
-        <v>-64.3821216</v>
+        <v>-65.33805480000001</v>
       </c>
       <c r="O90">
-        <v>-6.438212160000001</v>
+        <v>-6.533805480000002</v>
       </c>
       <c r="P90">
-        <v>-57.94390944000001</v>
+        <v>-58.80424932000001</v>
       </c>
       <c r="Q90">
-        <v>-52.38390944</v>
+        <v>-53.24424932000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2758013618261906</v>
+        <v>0.2967105765376624</v>
       </c>
       <c r="T90">
-        <v>4.6100690907446</v>
+        <v>5.029166280812291</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02346588462647619</v>
+        <v>0.02320222300145959</v>
       </c>
       <c r="W90">
-        <v>0.2302667444050769</v>
+        <v>0.2303289158162558</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2346588462647617</v>
+        <v>0.232022230014596</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2376308984956106</v>
+        <v>0.2395308984956106</v>
       </c>
       <c r="C91">
-        <v>-277.5883540997064</v>
+        <v>-282.1937040807368</v>
       </c>
       <c r="D91">
-        <v>56.21764590029363</v>
+        <v>55.66629591926322</v>
       </c>
       <c r="E91">
-        <v>307.206</v>
+        <v>311.26</v>
       </c>
       <c r="F91">
-        <v>360.806</v>
+        <v>364.86</v>
       </c>
       <c r="G91">
         <v>27</v>
@@ -8749,37 +8749,37 @@
         <v>19.74</v>
       </c>
       <c r="M91">
-        <v>85.07805480000002</v>
+        <v>86.03398800000001</v>
       </c>
       <c r="N91">
-        <v>-65.33805480000001</v>
+        <v>-66.29398800000001</v>
       </c>
       <c r="O91">
-        <v>-6.533805480000002</v>
+        <v>-6.629398800000001</v>
       </c>
       <c r="P91">
-        <v>-58.80424932000001</v>
+        <v>-59.66458920000001</v>
       </c>
       <c r="Q91">
-        <v>-53.24424932000001</v>
+        <v>-54.10458920000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2967105765376624</v>
+        <v>0.3218016341914287</v>
       </c>
       <c r="T91">
-        <v>5.029166280812291</v>
+        <v>5.53208290889352</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02320222300145959</v>
+        <v>0.0229444205236656</v>
       </c>
       <c r="W91">
-        <v>0.2303289158162558</v>
+        <v>0.2303897056405197</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.232022230014596</v>
+        <v>0.2294442052366559</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2395308984956106</v>
+        <v>0.2414308984956106</v>
       </c>
       <c r="C92">
-        <v>-282.1937040807368</v>
+        <v>-286.7883444553398</v>
       </c>
       <c r="D92">
-        <v>55.66629591926322</v>
+        <v>55.12565554466021</v>
       </c>
       <c r="E92">
-        <v>311.26</v>
+        <v>315.314</v>
       </c>
       <c r="F92">
-        <v>364.86</v>
+        <v>368.914</v>
       </c>
       <c r="G92">
         <v>27</v>
@@ -8831,37 +8831,37 @@
         <v>19.74</v>
       </c>
       <c r="M92">
-        <v>86.03398800000001</v>
+        <v>86.98992120000001</v>
       </c>
       <c r="N92">
-        <v>-66.29398800000001</v>
+        <v>-67.24992120000002</v>
       </c>
       <c r="O92">
-        <v>-6.629398800000001</v>
+        <v>-6.724992120000002</v>
       </c>
       <c r="P92">
-        <v>-59.66458920000001</v>
+        <v>-60.52492908000001</v>
       </c>
       <c r="Q92">
-        <v>-54.10458920000001</v>
+        <v>-54.96492908000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3218016341914287</v>
+        <v>0.3524684824349208</v>
       </c>
       <c r="T92">
-        <v>5.53208290889352</v>
+        <v>6.146758787659468</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0229444205236656</v>
+        <v>0.02269228403439455</v>
       </c>
       <c r="W92">
-        <v>0.2303897056405197</v>
+        <v>0.2304491594246898</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2294442052366559</v>
+        <v>0.2269228403439454</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2414308984956106</v>
+        <v>0.2433308984956106</v>
       </c>
       <c r="C93">
-        <v>-286.7883444553398</v>
+        <v>-291.3725842625424</v>
       </c>
       <c r="D93">
-        <v>55.12565554466021</v>
+        <v>54.59541573745768</v>
       </c>
       <c r="E93">
-        <v>315.314</v>
+        <v>319.3680000000001</v>
       </c>
       <c r="F93">
-        <v>368.914</v>
+        <v>372.9680000000001</v>
       </c>
       <c r="G93">
         <v>27</v>
@@ -8913,37 +8913,37 @@
         <v>19.74</v>
       </c>
       <c r="M93">
-        <v>86.98992120000001</v>
+        <v>87.94585440000002</v>
       </c>
       <c r="N93">
-        <v>-67.24992120000002</v>
+        <v>-68.20585440000002</v>
       </c>
       <c r="O93">
-        <v>-6.724992120000002</v>
+        <v>-6.820585440000002</v>
       </c>
       <c r="P93">
-        <v>-60.52492908000001</v>
+        <v>-61.38526896000002</v>
       </c>
       <c r="Q93">
-        <v>-54.96492908000001</v>
+        <v>-55.82526896000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3524684824349208</v>
+        <v>0.390802042739286</v>
       </c>
       <c r="T93">
-        <v>6.146758787659468</v>
+        <v>6.915103636116903</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02269228403439455</v>
+        <v>0.02244562877315113</v>
       </c>
       <c r="W93">
-        <v>0.2304491594246898</v>
+        <v>0.230507320735291</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2269228403439454</v>
+        <v>0.2244562877315112</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2433308984956106</v>
+        <v>0.2452308984956106</v>
       </c>
       <c r="C94">
-        <v>-291.3725842625424</v>
+        <v>-295.9467207643767</v>
       </c>
       <c r="D94">
-        <v>54.59541573745768</v>
+        <v>54.07527923562338</v>
       </c>
       <c r="E94">
-        <v>319.3680000000001</v>
+        <v>323.422</v>
       </c>
       <c r="F94">
-        <v>372.9680000000001</v>
+        <v>377.022</v>
       </c>
       <c r="G94">
         <v>27</v>
@@ -8995,37 +8995,37 @@
         <v>19.74</v>
       </c>
       <c r="M94">
-        <v>87.94585440000002</v>
+        <v>88.90178760000002</v>
       </c>
       <c r="N94">
-        <v>-68.20585440000002</v>
+        <v>-69.16178760000003</v>
       </c>
       <c r="O94">
-        <v>-6.820585440000002</v>
+        <v>-6.916178760000003</v>
       </c>
       <c r="P94">
-        <v>-61.38526896000002</v>
+        <v>-62.24560884000002</v>
       </c>
       <c r="Q94">
-        <v>-55.82526896000002</v>
+        <v>-56.68560884000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.390802042739286</v>
+        <v>0.4400880488448983</v>
       </c>
       <c r="T94">
-        <v>6.915103636116903</v>
+        <v>7.902975584133604</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02244562877315113</v>
+        <v>0.022204277926128</v>
       </c>
       <c r="W94">
-        <v>0.230507320735291</v>
+        <v>0.230564231265019</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2244562877315112</v>
+        <v>0.2220427792612799</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2452308984956106</v>
+        <v>0.2471308984956105</v>
       </c>
       <c r="C95">
-        <v>-295.9467207643767</v>
+        <v>-300.5110400015896</v>
       </c>
       <c r="D95">
-        <v>54.07527923562338</v>
+        <v>53.56495999841046</v>
       </c>
       <c r="E95">
-        <v>323.422</v>
+        <v>327.4760000000001</v>
       </c>
       <c r="F95">
-        <v>377.022</v>
+        <v>381.0760000000001</v>
       </c>
       <c r="G95">
         <v>27</v>
@@ -9077,37 +9077,37 @@
         <v>19.74</v>
       </c>
       <c r="M95">
-        <v>88.90178760000002</v>
+        <v>89.85772080000002</v>
       </c>
       <c r="N95">
-        <v>-69.16178760000003</v>
+        <v>-70.11772080000003</v>
       </c>
       <c r="O95">
-        <v>-6.916178760000003</v>
+        <v>-7.011772080000004</v>
       </c>
       <c r="P95">
-        <v>-62.24560884000002</v>
+        <v>-63.10594872000003</v>
       </c>
       <c r="Q95">
-        <v>-56.68560884000002</v>
+        <v>-57.54594872000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4400880488448983</v>
+        <v>0.5058027236523814</v>
       </c>
       <c r="T95">
-        <v>7.902975584133604</v>
+        <v>9.220138181489206</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.022204277926128</v>
+        <v>0.02196806220350962</v>
       </c>
       <c r="W95">
-        <v>0.230564231265019</v>
+        <v>0.2306199309324124</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2220427792612799</v>
+        <v>0.2196806220350961</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2471308984956105</v>
+        <v>0.2490308984956106</v>
       </c>
       <c r="C96">
-        <v>-300.5110400015896</v>
+        <v>-305.0658173181805</v>
       </c>
       <c r="D96">
-        <v>53.56495999841046</v>
+        <v>53.0641826818196</v>
       </c>
       <c r="E96">
-        <v>327.4760000000001</v>
+        <v>331.53</v>
       </c>
       <c r="F96">
-        <v>381.0760000000001</v>
+        <v>385.1300000000001</v>
       </c>
       <c r="G96">
         <v>27</v>
@@ -9159,37 +9159,37 @@
         <v>19.74</v>
       </c>
       <c r="M96">
-        <v>89.85772080000002</v>
+        <v>90.81365400000001</v>
       </c>
       <c r="N96">
-        <v>-70.11772080000003</v>
+        <v>-71.073654</v>
       </c>
       <c r="O96">
-        <v>-7.011772080000004</v>
+        <v>-7.107365400000001</v>
       </c>
       <c r="P96">
-        <v>-63.10594872000003</v>
+        <v>-63.96628860000001</v>
       </c>
       <c r="Q96">
-        <v>-57.54594872000003</v>
+        <v>-58.4062886</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5058027236523814</v>
+        <v>0.597803268382858</v>
       </c>
       <c r="T96">
-        <v>9.220138181489206</v>
+        <v>11.06416581778705</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02196806220350962</v>
+        <v>0.02173681944347268</v>
       </c>
       <c r="W96">
-        <v>0.2306199309324124</v>
+        <v>0.2306744579752291</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2196806220350961</v>
+        <v>0.2173681944347268</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2490308984956106</v>
+        <v>0.2509308984956106</v>
       </c>
       <c r="C97">
-        <v>-305.0658173181805</v>
+        <v>-309.6113178567871</v>
       </c>
       <c r="D97">
-        <v>53.0641826818196</v>
+        <v>52.57268214321297</v>
       </c>
       <c r="E97">
-        <v>331.53</v>
+        <v>335.5840000000001</v>
       </c>
       <c r="F97">
-        <v>385.1300000000001</v>
+        <v>389.1840000000001</v>
       </c>
       <c r="G97">
         <v>27</v>
@@ -9241,37 +9241,37 @@
         <v>19.74</v>
       </c>
       <c r="M97">
-        <v>90.81365400000001</v>
+        <v>91.76958720000002</v>
       </c>
       <c r="N97">
-        <v>-71.073654</v>
+        <v>-72.02958720000001</v>
       </c>
       <c r="O97">
-        <v>-7.107365400000001</v>
+        <v>-7.202958720000002</v>
       </c>
       <c r="P97">
-        <v>-63.96628860000001</v>
+        <v>-64.82662848000001</v>
       </c>
       <c r="Q97">
-        <v>-58.4062886</v>
+        <v>-59.26662848000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.597803268382858</v>
+        <v>0.7358040854785728</v>
       </c>
       <c r="T97">
-        <v>11.06416581778705</v>
+        <v>13.83020727223382</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02173681944347268</v>
+        <v>0.0215103942409365</v>
       </c>
       <c r="W97">
-        <v>0.2306744579752291</v>
+        <v>0.2307278490379872</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2173681944347268</v>
+        <v>0.215103942409365</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2509308984956106</v>
+        <v>0.2528308984956106</v>
       </c>
       <c r="C98">
-        <v>-309.6113178567871</v>
+        <v>-314.1477970267947</v>
       </c>
       <c r="D98">
-        <v>52.57268214321297</v>
+        <v>52.09020297320527</v>
       </c>
       <c r="E98">
-        <v>335.584</v>
+        <v>339.638</v>
       </c>
       <c r="F98">
-        <v>389.184</v>
+        <v>393.238</v>
       </c>
       <c r="G98">
         <v>27</v>
@@ -9323,37 +9323,37 @@
         <v>19.74</v>
       </c>
       <c r="M98">
-        <v>91.7695872</v>
+        <v>92.72552040000001</v>
       </c>
       <c r="N98">
-        <v>-72.02958720000001</v>
+        <v>-72.98552040000001</v>
       </c>
       <c r="O98">
-        <v>-7.202958720000002</v>
+        <v>-7.298552040000001</v>
       </c>
       <c r="P98">
-        <v>-64.82662848000001</v>
+        <v>-65.68696836000001</v>
       </c>
       <c r="Q98">
-        <v>-59.26662848000001</v>
+        <v>-60.12696836000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.735804085478571</v>
+        <v>0.9658054473047614</v>
       </c>
       <c r="T98">
-        <v>13.83020727223379</v>
+        <v>18.44027636297838</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0215103942409365</v>
+        <v>0.02128863759927736</v>
       </c>
       <c r="W98">
-        <v>0.2307278490379872</v>
+        <v>0.2307801392540904</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2151039424093649</v>
+        <v>0.2128863759927735</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2528308984956106</v>
+        <v>0.2547308984956106</v>
       </c>
       <c r="C99">
-        <v>-314.1477970267947</v>
+        <v>-318.6755009469029</v>
       </c>
       <c r="D99">
-        <v>52.09020297320527</v>
+        <v>51.61649905309712</v>
       </c>
       <c r="E99">
-        <v>339.638</v>
+        <v>343.692</v>
       </c>
       <c r="F99">
-        <v>393.238</v>
+        <v>397.292</v>
       </c>
       <c r="G99">
         <v>27</v>
@@ -9405,37 +9405,37 @@
         <v>19.74</v>
       </c>
       <c r="M99">
-        <v>92.72552040000001</v>
+        <v>93.68145360000001</v>
       </c>
       <c r="N99">
-        <v>-72.98552040000001</v>
+        <v>-73.94145360000002</v>
       </c>
       <c r="O99">
-        <v>-7.298552040000001</v>
+        <v>-7.394145360000002</v>
       </c>
       <c r="P99">
-        <v>-65.68696836000001</v>
+        <v>-66.54730824000002</v>
       </c>
       <c r="Q99">
-        <v>-60.12696836000001</v>
+        <v>-60.98730824000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9658054473047614</v>
+        <v>1.425808170957142</v>
       </c>
       <c r="T99">
-        <v>18.44027636297838</v>
+        <v>27.66041454446757</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02128863759927736</v>
+        <v>0.02107140660336637</v>
       </c>
       <c r="W99">
-        <v>0.2307801392540904</v>
+        <v>0.2308313623229262</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2128863759927735</v>
+        <v>0.2107140660336636</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2547308984956106</v>
+        <v>0.2566308984956105</v>
       </c>
       <c r="C100">
-        <v>-318.6755009469029</v>
+        <v>-323.1946668637617</v>
       </c>
       <c r="D100">
-        <v>51.61649905309712</v>
+        <v>51.15133313623829</v>
       </c>
       <c r="E100">
-        <v>343.692</v>
+        <v>347.746</v>
       </c>
       <c r="F100">
-        <v>397.292</v>
+        <v>401.346</v>
       </c>
       <c r="G100">
         <v>27</v>
@@ -9487,37 +9487,37 @@
         <v>19.74</v>
       </c>
       <c r="M100">
-        <v>93.68145360000001</v>
+        <v>94.6373868</v>
       </c>
       <c r="N100">
-        <v>-73.94145360000002</v>
+        <v>-74.89738679999999</v>
       </c>
       <c r="O100">
-        <v>-7.394145360000002</v>
+        <v>-7.489738679999999</v>
       </c>
       <c r="P100">
-        <v>-66.54730824000002</v>
+        <v>-67.40764811999999</v>
       </c>
       <c r="Q100">
-        <v>-60.98730824000002</v>
+        <v>-61.84764811999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.425808170957142</v>
+        <v>2.805816341914284</v>
       </c>
       <c r="T100">
-        <v>27.66041454446757</v>
+        <v>55.32082908893515</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02107140660336637</v>
+        <v>0.02085856411242328</v>
       </c>
       <c r="W100">
-        <v>0.2308313623229262</v>
+        <v>0.2308815505822906</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2107140660336636</v>
+        <v>0.2085856411242328</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2566308984956105</v>
-      </c>
-      <c r="C101">
-        <v>-323.1946668637617</v>
-      </c>
-      <c r="D101">
-        <v>51.15133313623829</v>
-      </c>
-      <c r="E101">
-        <v>347.746</v>
-      </c>
-      <c r="F101">
-        <v>401.346</v>
-      </c>
-      <c r="G101">
-        <v>27</v>
-      </c>
-      <c r="H101">
-        <v>351.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>25.3</v>
-      </c>
-      <c r="K101">
-        <v>5.56</v>
-      </c>
-      <c r="L101">
-        <v>19.74</v>
-      </c>
-      <c r="M101">
-        <v>94.6373868</v>
-      </c>
-      <c r="N101">
-        <v>-74.89738679999999</v>
-      </c>
-      <c r="O101">
-        <v>-7.489738679999999</v>
-      </c>
-      <c r="P101">
-        <v>-67.40764811999999</v>
-      </c>
-      <c r="Q101">
-        <v>-61.84764811999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.805816341914284</v>
-      </c>
-      <c r="T101">
-        <v>55.32082908893515</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02085856411242328</v>
-      </c>
-      <c r="W101">
-        <v>0.2308815505822906</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2085856411242328</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
